--- a/data-collection/tomcat.xlsx
+++ b/data-collection/tomcat.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://politechnikawroclawska-my.sharepoint.com/personal/260364_student_pwr_edu_pl/Documents/Semestr10-3mgr/dyplomowe/ai/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://politechnikawroclawska-my.sharepoint.com/personal/260364_student_pwr_edu_pl/Documents/Semestr10-3mgr/dyplomowe/ai/data-collection/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="728" documentId="11_F25DC773A252ABDACC1048A6391B61545ADE58F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56B9D2E7-44E5-4BA3-A17A-A827999FEC2A}"/>
+  <xr:revisionPtr revIDLastSave="769" documentId="11_F25DC773A252ABDACC1048A6391B61545ADE58F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C43708C0-3CA3-4E7A-9C08-53A7DA8C9ADB}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3960" yWindow="-11640" windowWidth="20640" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4266" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4597" uniqueCount="615">
   <si>
     <t>Wersja</t>
   </si>
@@ -1171,13 +1171,748 @@
   </si>
   <si>
     <t>Mediana</t>
+  </si>
+  <si>
+    <t>Data</t>
+  </si>
+  <si>
+    <t>Dec 09, 2024</t>
+  </si>
+  <si>
+    <t>Oct 09, 2024</t>
+  </si>
+  <si>
+    <t>Sep 10, 2024</t>
+  </si>
+  <si>
+    <t>Aug 06, 2024</t>
+  </si>
+  <si>
+    <t>Apr 16, 2024</t>
+  </si>
+  <si>
+    <t>Feb 19, 2024</t>
+  </si>
+  <si>
+    <t>Jan 09, 2024</t>
+  </si>
+  <si>
+    <t>Dec 12, 2023</t>
+  </si>
+  <si>
+    <t>Nov 15, 2023</t>
+  </si>
+  <si>
+    <t>Oct 10, 2023</t>
+  </si>
+  <si>
+    <t>Aug 25, 2023</t>
+  </si>
+  <si>
+    <t>Aug 14, 2023</t>
+  </si>
+  <si>
+    <t>Jul 10, 2023</t>
+  </si>
+  <si>
+    <t>Apr 19, 2023</t>
+  </si>
+  <si>
+    <t>Feb 23, 2023</t>
+  </si>
+  <si>
+    <t>Dec 01, 2022</t>
+  </si>
+  <si>
+    <t>Nov 11, 2024</t>
+  </si>
+  <si>
+    <t>Sep 17, 2024</t>
+  </si>
+  <si>
+    <t>Jul 12, 2024</t>
+  </si>
+  <si>
+    <t>Jun 19, 2024</t>
+  </si>
+  <si>
+    <t>May 13, 2024</t>
+  </si>
+  <si>
+    <t>Apr 23, 2024</t>
+  </si>
+  <si>
+    <t>Mar 26, 2024</t>
+  </si>
+  <si>
+    <t>Oct 16, 2023</t>
+  </si>
+  <si>
+    <t>Jun 12, 2023</t>
+  </si>
+  <si>
+    <t>May 20, 2023</t>
+  </si>
+  <si>
+    <t>Mar 04, 2023</t>
+  </si>
+  <si>
+    <t>Feb 24, 2023</t>
+  </si>
+  <si>
+    <t>Jan 13, 2023</t>
+  </si>
+  <si>
+    <t>Dec 05, 2022</t>
+  </si>
+  <si>
+    <t>Nov 14, 2022</t>
+  </si>
+  <si>
+    <t>Oct 11, 2022</t>
+  </si>
+  <si>
+    <t>Sep 26, 2022</t>
+  </si>
+  <si>
+    <t>Jul 20, 2022</t>
+  </si>
+  <si>
+    <t>Jun 09, 2022</t>
+  </si>
+  <si>
+    <t>May 16, 2022</t>
+  </si>
+  <si>
+    <t>Apr 02, 2022</t>
+  </si>
+  <si>
+    <t>Mar 14, 2022</t>
+  </si>
+  <si>
+    <t>Feb 28, 2022</t>
+  </si>
+  <si>
+    <t>Jan 20, 2022</t>
+  </si>
+  <si>
+    <t>Dec 08, 2021</t>
+  </si>
+  <si>
+    <t>Nov 15, 2021</t>
+  </si>
+  <si>
+    <t>Oct 01, 2021</t>
+  </si>
+  <si>
+    <t>Sep 10, 2021</t>
+  </si>
+  <si>
+    <t>Aug 06, 2021</t>
+  </si>
+  <si>
+    <t>Jul 02, 2021</t>
+  </si>
+  <si>
+    <t>Jun 15, 2021</t>
+  </si>
+  <si>
+    <t>Oct 10, 2022</t>
+  </si>
+  <si>
+    <t>Sep 27, 2022</t>
+  </si>
+  <si>
+    <t>Jul 26, 2022</t>
+  </si>
+  <si>
+    <t>Jun 11, 2022</t>
+  </si>
+  <si>
+    <t>Aug 05, 2021</t>
+  </si>
+  <si>
+    <t>Jul 05, 2021</t>
+  </si>
+  <si>
+    <t>May 13, 2021</t>
+  </si>
+  <si>
+    <t>Apr 06, 2021</t>
+  </si>
+  <si>
+    <t>Mar 10, 2021</t>
+  </si>
+  <si>
+    <t>Feb 02, 2021</t>
+  </si>
+  <si>
+    <t>Dec 08, 2020</t>
+  </si>
+  <si>
+    <t>Nov 17, 2020</t>
+  </si>
+  <si>
+    <t>Oct 09, 2020</t>
+  </si>
+  <si>
+    <t>Jul 05, 2020</t>
+  </si>
+  <si>
+    <t>Jun 07, 2020</t>
+  </si>
+  <si>
+    <t>May 11, 2020</t>
+  </si>
+  <si>
+    <t>Apr 08, 2020</t>
+  </si>
+  <si>
+    <t>Mar 16, 2020</t>
+  </si>
+  <si>
+    <t>Nov 09, 2024</t>
+  </si>
+  <si>
+    <t>Oct 08, 2024</t>
+  </si>
+  <si>
+    <t>Jul 08, 2024</t>
+  </si>
+  <si>
+    <t>May 07, 2024</t>
+  </si>
+  <si>
+    <t>Mar 15, 2024</t>
+  </si>
+  <si>
+    <t>Oct 13, 2023</t>
+  </si>
+  <si>
+    <t>Aug 15, 2023</t>
+  </si>
+  <si>
+    <t>Jun 09, 2023</t>
+  </si>
+  <si>
+    <t>May 10, 2023</t>
+  </si>
+  <si>
+    <t>Apr 18, 2023</t>
+  </si>
+  <si>
+    <t>Mar 03, 2023</t>
+  </si>
+  <si>
+    <t>Oct 07, 2022</t>
+  </si>
+  <si>
+    <t>Oct 02, 2021</t>
+  </si>
+  <si>
+    <t>Sep 15, 2020</t>
+  </si>
+  <si>
+    <t>Feb 11, 2020</t>
+  </si>
+  <si>
+    <t>Dec 07, 2019</t>
+  </si>
+  <si>
+    <t>Nov 16, 2019</t>
+  </si>
+  <si>
+    <t>Oct 07, 2019</t>
+  </si>
+  <si>
+    <t>Sep 16, 2019</t>
+  </si>
+  <si>
+    <t>Aug 17, 2019</t>
+  </si>
+  <si>
+    <t>Jul 09, 2019</t>
+  </si>
+  <si>
+    <t>Jun 08, 2019</t>
+  </si>
+  <si>
+    <t>May 15, 2019</t>
+  </si>
+  <si>
+    <t>Apr 14, 2019</t>
+  </si>
+  <si>
+    <t>Mar 19, 2019</t>
+  </si>
+  <si>
+    <t>Feb 08, 2019</t>
+  </si>
+  <si>
+    <t>Dec 12, 2018</t>
+  </si>
+  <si>
+    <t>Nov 02, 2018</t>
+  </si>
+  <si>
+    <t>Sep 10, 2018</t>
+  </si>
+  <si>
+    <t>Aug 11, 2018</t>
+  </si>
+  <si>
+    <t>Jun 20, 2018</t>
+  </si>
+  <si>
+    <t>Apr 27, 2018</t>
+  </si>
+  <si>
+    <t>Apr 03, 2018</t>
+  </si>
+  <si>
+    <t>Mar 05, 2018</t>
+  </si>
+  <si>
+    <t>Feb 06, 2018</t>
+  </si>
+  <si>
+    <t>Jan 18, 2018</t>
+  </si>
+  <si>
+    <t>Nov 25, 2017</t>
+  </si>
+  <si>
+    <t>Sep 27, 2017</t>
+  </si>
+  <si>
+    <t>Sep 13, 2017</t>
+  </si>
+  <si>
+    <t>Aug 02, 2017</t>
+  </si>
+  <si>
+    <t>Jul 24, 2017</t>
+  </si>
+  <si>
+    <t>Jun 21, 2017</t>
+  </si>
+  <si>
+    <t>Mar 27, 2017</t>
+  </si>
+  <si>
+    <t>Mar 08, 2017</t>
+  </si>
+  <si>
+    <t>Jan 10, 2017</t>
+  </si>
+  <si>
+    <t>Dec 05, 2016</t>
+  </si>
+  <si>
+    <t>Nov 03, 2016</t>
+  </si>
+  <si>
+    <t>Oct 06, 2016</t>
+  </si>
+  <si>
+    <t>Aug 31, 2016</t>
+  </si>
+  <si>
+    <t>May 11, 2016</t>
+  </si>
+  <si>
+    <t>Jan 19, 2023</t>
+  </si>
+  <si>
+    <t>Nov 22, 2022</t>
+  </si>
+  <si>
+    <t>Aug 13, 2022</t>
+  </si>
+  <si>
+    <t>May 24, 2022</t>
+  </si>
+  <si>
+    <t>Mar 17, 2022</t>
+  </si>
+  <si>
+    <t>Mar 01, 2022</t>
+  </si>
+  <si>
+    <t>Nov 17, 2021</t>
+  </si>
+  <si>
+    <t>Oct 06, 2021</t>
+  </si>
+  <si>
+    <t>Sep 13, 2021</t>
+  </si>
+  <si>
+    <t>Aug 16, 2021</t>
+  </si>
+  <si>
+    <t>Jun 16, 2021</t>
+  </si>
+  <si>
+    <t>Feb 03, 2021</t>
+  </si>
+  <si>
+    <t>Nov 17, 2019</t>
+  </si>
+  <si>
+    <t>Oct 12, 2019</t>
+  </si>
+  <si>
+    <t>Aug 21, 2019</t>
+  </si>
+  <si>
+    <t>Apr 12, 2019</t>
+  </si>
+  <si>
+    <t>Mar 20, 2019</t>
+  </si>
+  <si>
+    <t>Dec 18, 2018</t>
+  </si>
+  <si>
+    <t>Nov 08, 2018</t>
+  </si>
+  <si>
+    <t>Aug 12, 2018</t>
+  </si>
+  <si>
+    <t>Nov 27, 2017</t>
+  </si>
+  <si>
+    <t>Sep 28, 2017</t>
+  </si>
+  <si>
+    <t>May 05, 2017</t>
+  </si>
+  <si>
+    <t>Apr 13, 2017</t>
+  </si>
+  <si>
+    <t>Jul 06, 2016</t>
+  </si>
+  <si>
+    <t>Jun 09, 2016</t>
+  </si>
+  <si>
+    <t>Mar 17, 2016</t>
+  </si>
+  <si>
+    <t>Jun 29, 2018</t>
+  </si>
+  <si>
+    <t>Apr 28, 2018</t>
+  </si>
+  <si>
+    <t>Apr 09, 2018</t>
+  </si>
+  <si>
+    <t>Feb 07, 2018</t>
+  </si>
+  <si>
+    <t>Jan 19, 2018</t>
+  </si>
+  <si>
+    <t>Nov 30, 2017</t>
+  </si>
+  <si>
+    <t>Sep 29, 2017</t>
+  </si>
+  <si>
+    <t>Aug 10, 2017</t>
+  </si>
+  <si>
+    <t>Jun 26, 2017</t>
+  </si>
+  <si>
+    <t>May 10, 2017</t>
+  </si>
+  <si>
+    <t>Mar 28, 2017</t>
+  </si>
+  <si>
+    <t>Jan 18, 2017</t>
+  </si>
+  <si>
+    <t>Nov 09, 2016</t>
+  </si>
+  <si>
+    <t>Sep 01, 2016</t>
+  </si>
+  <si>
+    <t>Mar 18, 2016</t>
+  </si>
+  <si>
+    <t>Feb 02, 2016</t>
+  </si>
+  <si>
+    <t>Dec 01, 2015</t>
+  </si>
+  <si>
+    <t>Nov 20, 2015</t>
+  </si>
+  <si>
+    <t>Oct 07, 2015</t>
+  </si>
+  <si>
+    <t>Sep 28, 2015</t>
+  </si>
+  <si>
+    <t>Aug 18, 2015</t>
+  </si>
+  <si>
+    <t>Jul 01, 2015</t>
+  </si>
+  <si>
+    <t>May 19, 2015</t>
+  </si>
+  <si>
+    <t>Apr 29, 2015</t>
+  </si>
+  <si>
+    <t>Mar 23, 2015</t>
+  </si>
+  <si>
+    <t>Feb 15, 2015</t>
+  </si>
+  <si>
+    <t>Jan 23, 2015</t>
+  </si>
+  <si>
+    <t>Jan 09, 2015</t>
+  </si>
+  <si>
+    <t>Nov 02, 2014</t>
+  </si>
+  <si>
+    <t>Sep 24, 2014</t>
+  </si>
+  <si>
+    <t>Aug 29, 2014</t>
+  </si>
+  <si>
+    <t>Aug 15, 2014</t>
+  </si>
+  <si>
+    <t>Jun 19, 2014</t>
+  </si>
+  <si>
+    <t>May 16, 2014</t>
+  </si>
+  <si>
+    <t>Mar 24, 2014</t>
+  </si>
+  <si>
+    <t>Feb 07, 2014</t>
+  </si>
+  <si>
+    <t>Jan 29, 2014</t>
+  </si>
+  <si>
+    <t>Dec 19, 2013</t>
+  </si>
+  <si>
+    <t>Sep 20, 2020</t>
+  </si>
+  <si>
+    <t>Jul 07, 2020</t>
+  </si>
+  <si>
+    <t>May 16, 2020</t>
+  </si>
+  <si>
+    <t>Mar 19, 2020</t>
+  </si>
+  <si>
+    <t>Feb 14, 2020</t>
+  </si>
+  <si>
+    <t>Dec 11, 2019</t>
+  </si>
+  <si>
+    <t>Jul 29, 2019</t>
+  </si>
+  <si>
+    <t>Feb 21, 2019</t>
+  </si>
+  <si>
+    <t>Nov 15, 2018</t>
+  </si>
+  <si>
+    <t>Sep 19, 2018</t>
+  </si>
+  <si>
+    <t>Jul 02, 2018</t>
+  </si>
+  <si>
+    <t>May 07, 2018</t>
+  </si>
+  <si>
+    <t>Aug 11, 2017</t>
+  </si>
+  <si>
+    <t>Mar 09, 2017</t>
+  </si>
+  <si>
+    <t>Nov 07, 2016</t>
+  </si>
+  <si>
+    <t>Sep 14, 2016</t>
+  </si>
+  <si>
+    <t>Jun 15, 2016</t>
+  </si>
+  <si>
+    <t>Apr 11, 2016</t>
+  </si>
+  <si>
+    <t>Feb 08, 2016</t>
+  </si>
+  <si>
+    <t>Dec 07, 2015</t>
+  </si>
+  <si>
+    <t>Oct 09, 2015</t>
+  </si>
+  <si>
+    <t>Aug 19, 2015</t>
+  </si>
+  <si>
+    <t>Jun 30, 2015</t>
+  </si>
+  <si>
+    <t>May 07, 2015</t>
+  </si>
+  <si>
+    <t>Mar 27, 2015</t>
+  </si>
+  <si>
+    <t>Jan 28, 2015</t>
+  </si>
+  <si>
+    <t>Nov 03, 2014</t>
+  </si>
+  <si>
+    <t>Sep 28, 2014</t>
+  </si>
+  <si>
+    <t>Jul 18, 2014</t>
+  </si>
+  <si>
+    <t>May 20, 2014</t>
+  </si>
+  <si>
+    <t>Mar 25, 2014</t>
+  </si>
+  <si>
+    <t>Feb 13, 2014</t>
+  </si>
+  <si>
+    <t>Oct 18, 2013</t>
+  </si>
+  <si>
+    <t>Jul 02, 2013</t>
+  </si>
+  <si>
+    <t>Jun 06, 2013</t>
+  </si>
+  <si>
+    <t>May 05, 2013</t>
+  </si>
+  <si>
+    <t>Mar 22, 2013</t>
+  </si>
+  <si>
+    <t>Feb 12, 2013</t>
+  </si>
+  <si>
+    <t>Jan 10, 2013</t>
+  </si>
+  <si>
+    <t>Dec 04, 2012</t>
+  </si>
+  <si>
+    <t>Nov 18, 2012</t>
+  </si>
+  <si>
+    <t>Oct 03, 2012</t>
+  </si>
+  <si>
+    <t>Sep 02, 2012</t>
+  </si>
+  <si>
+    <t>Jul 03, 2012</t>
+  </si>
+  <si>
+    <t>Jun 15, 2012</t>
+  </si>
+  <si>
+    <t>Mar 31, 2012</t>
+  </si>
+  <si>
+    <t>Feb 17, 2012</t>
+  </si>
+  <si>
+    <t>Jan 17, 2012</t>
+  </si>
+  <si>
+    <t>Nov 24, 2011</t>
+  </si>
+  <si>
+    <t>Oct 10, 2011</t>
+  </si>
+  <si>
+    <t>Sep 01, 2011</t>
+  </si>
+  <si>
+    <t>Aug 16, 2011</t>
+  </si>
+  <si>
+    <t>Jul 25, 2011</t>
+  </si>
+  <si>
+    <t>Jun 17, 2011</t>
+  </si>
+  <si>
+    <t>May 12, 2011</t>
+  </si>
+  <si>
+    <t>Apr 17, 2011</t>
+  </si>
+  <si>
+    <t>Mar 12, 2011</t>
+  </si>
+  <si>
+    <t>Feb 16, 2011</t>
+  </si>
+  <si>
+    <t>Jan 17, 2011</t>
+  </si>
+  <si>
+    <t>Dec 02, 2010</t>
+  </si>
+  <si>
+    <t>Oct 26, 2010</t>
+  </si>
+  <si>
+    <t>Aug 22, 2010</t>
+  </si>
+  <si>
+    <t>Jul 12, 2010</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1191,6 +1926,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1273,12 +2014,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1297,6 +2040,9 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="20% — akcent 3" xfId="1" builtinId="38"/>
@@ -1313,6 +2059,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1578,16 +2328,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R3911"/>
+  <dimension ref="A1:AE3911"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="14.36328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.7265625" style="1"/>
     <col min="8" max="8" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.36328125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14.36328125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="26" max="30" width="8.7265625" style="5"/>
+    <col min="31" max="31" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1600,8 +2354,13 @@
       <c r="D1" s="1" t="s">
         <v>370</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z1"/>
+      <c r="AA1"/>
+      <c r="AB1"/>
+      <c r="AC1"/>
+      <c r="AD1"/>
+    </row>
+    <row r="2" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1619,12 +2378,20 @@
         <f t="array" ref="H2:H330">_xlfn._xlws.FILTER(A:A, LEN(A:A) &gt; 0)</f>
         <v>Wersja</v>
       </c>
-      <c r="I2" t="str" cm="1">
-        <f t="array" ref="I2:I330">_xlfn._xlws.FILTER(D:D, LEN(A:A) &gt; 0)</f>
+      <c r="I2" t="s">
+        <v>371</v>
+      </c>
+      <c r="J2" t="str" cm="1">
+        <f t="array" ref="J2:J330">_xlfn._xlws.FILTER(D:D, LEN(A:A) &gt; 0)</f>
         <v>Mediana</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z2"/>
+      <c r="AA2"/>
+      <c r="AB2"/>
+      <c r="AC2"/>
+      <c r="AD2"/>
+    </row>
+    <row r="3" spans="1:30" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>5</v>
       </c>
@@ -1637,11 +2404,19 @@
       <c r="H3" t="str">
         <v>10.1.33</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="J3">
         <v>8.1</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z3"/>
+      <c r="AA3"/>
+      <c r="AB3"/>
+      <c r="AC3"/>
+      <c r="AD3"/>
+    </row>
+    <row r="4" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1658,11 +2433,19 @@
       <c r="H4" t="str">
         <v>10.1.31</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="J4">
         <v>8.1</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z4"/>
+      <c r="AA4"/>
+      <c r="AB4"/>
+      <c r="AC4"/>
+      <c r="AD4"/>
+    </row>
+    <row r="5" spans="1:30" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>5</v>
       </c>
@@ -1672,11 +2455,19 @@
       <c r="H5" t="str">
         <v>10.1.30</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="J5">
         <v>7.3</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z5"/>
+      <c r="AA5"/>
+      <c r="AB5"/>
+      <c r="AC5"/>
+      <c r="AD5"/>
+    </row>
+    <row r="6" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -1693,11 +2484,19 @@
       <c r="H6" t="str">
         <v>10.1.29</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="J6">
         <v>8.1</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z6"/>
+      <c r="AA6"/>
+      <c r="AB6"/>
+      <c r="AC6"/>
+      <c r="AD6"/>
+    </row>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>8</v>
       </c>
@@ -1707,11 +2506,19 @@
       <c r="H7" t="str">
         <v>10.1.28</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="J7">
         <v>8.1</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z7"/>
+      <c r="AA7"/>
+      <c r="AB7"/>
+      <c r="AC7"/>
+      <c r="AD7"/>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>5</v>
       </c>
@@ -1721,11 +2528,19 @@
       <c r="H8" t="str">
         <v>10.1.26</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="J8">
         <v>8.1</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z8"/>
+      <c r="AA8"/>
+      <c r="AB8"/>
+      <c r="AC8"/>
+      <c r="AD8"/>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -1742,11 +2557,19 @@
       <c r="H9" t="str">
         <v>10.1.25</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="J9">
         <v>8.1</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z9"/>
+      <c r="AA9"/>
+      <c r="AB9"/>
+      <c r="AC9"/>
+      <c r="AD9"/>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>8</v>
       </c>
@@ -1756,11 +2579,19 @@
       <c r="H10" t="str">
         <v>10.1.24</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="J10">
         <v>8.1</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z10"/>
+      <c r="AA10"/>
+      <c r="AB10"/>
+      <c r="AC10"/>
+      <c r="AD10"/>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>5</v>
       </c>
@@ -1770,11 +2601,19 @@
       <c r="H11" t="str">
         <v>10.1.23</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="J11">
         <v>8.1</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z11"/>
+      <c r="AA11"/>
+      <c r="AB11"/>
+      <c r="AC11"/>
+      <c r="AD11"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -1791,11 +2630,19 @@
       <c r="H12" t="str">
         <v>10.1.20</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="J12">
         <v>8.1</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z12"/>
+      <c r="AA12"/>
+      <c r="AB12"/>
+      <c r="AC12"/>
+      <c r="AD12"/>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>8</v>
       </c>
@@ -1805,11 +2652,19 @@
       <c r="H13" t="str">
         <v>10.1.19</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="J13">
         <v>8.1</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z13"/>
+      <c r="AA13"/>
+      <c r="AB13"/>
+      <c r="AC13"/>
+      <c r="AD13"/>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>5</v>
       </c>
@@ -1819,11 +2674,19 @@
       <c r="H14" t="str">
         <v>10.1.18</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="J14">
         <v>7.8</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z14"/>
+      <c r="AA14"/>
+      <c r="AB14"/>
+      <c r="AC14"/>
+      <c r="AD14"/>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>11</v>
       </c>
@@ -1840,11 +2703,19 @@
       <c r="H15" t="str">
         <v>10.1.17</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="J15">
         <v>7.8</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z15"/>
+      <c r="AA15"/>
+      <c r="AB15"/>
+      <c r="AC15"/>
+      <c r="AD15"/>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
         <v>5</v>
       </c>
@@ -1854,11 +2725,19 @@
       <c r="H16" t="str">
         <v>10.1.16</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="J16">
         <v>7.8</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z16"/>
+      <c r="AA16"/>
+      <c r="AB16"/>
+      <c r="AC16"/>
+      <c r="AD16"/>
+    </row>
+    <row r="17" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>12</v>
       </c>
@@ -1875,11 +2754,19 @@
       <c r="H17" t="str">
         <v>10.1.15</v>
       </c>
-      <c r="I17">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I17" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="J17">
+        <v>7.5</v>
+      </c>
+      <c r="Z17"/>
+      <c r="AA17"/>
+      <c r="AB17"/>
+      <c r="AC17"/>
+      <c r="AD17"/>
+    </row>
+    <row r="18" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
         <v>5</v>
       </c>
@@ -1889,11 +2776,19 @@
       <c r="H18" t="str">
         <v>10.1.14</v>
       </c>
-      <c r="I18">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I18" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="J18">
+        <v>7.5</v>
+      </c>
+      <c r="Z18"/>
+      <c r="AA18"/>
+      <c r="AB18"/>
+      <c r="AC18"/>
+      <c r="AD18"/>
+    </row>
+    <row r="19" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>13</v>
       </c>
@@ -1910,11 +2805,19 @@
       <c r="H19" t="str">
         <v>10.1.13</v>
       </c>
-      <c r="I19">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I19" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="J19">
+        <v>7.5</v>
+      </c>
+      <c r="Z19"/>
+      <c r="AA19"/>
+      <c r="AB19"/>
+      <c r="AC19"/>
+      <c r="AD19"/>
+    </row>
+    <row r="20" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
         <v>5</v>
       </c>
@@ -1924,11 +2827,19 @@
       <c r="H20" t="str">
         <v>10.1.12</v>
       </c>
-      <c r="I20">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I20" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="J20">
+        <v>7.5</v>
+      </c>
+      <c r="Z20"/>
+      <c r="AA20"/>
+      <c r="AB20"/>
+      <c r="AC20"/>
+      <c r="AD20"/>
+    </row>
+    <row r="21" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>14</v>
       </c>
@@ -1938,11 +2849,19 @@
       <c r="H21" t="str">
         <v>10.1.11</v>
       </c>
-      <c r="I21">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I21" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="J21">
+        <v>7.5</v>
+      </c>
+      <c r="Z21"/>
+      <c r="AA21"/>
+      <c r="AB21"/>
+      <c r="AC21"/>
+      <c r="AD21"/>
+    </row>
+    <row r="22" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>15</v>
       </c>
@@ -1959,11 +2878,19 @@
       <c r="H22" t="str">
         <v>10.1.10</v>
       </c>
-      <c r="I22">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I22" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="J22">
+        <v>7.5</v>
+      </c>
+      <c r="Z22"/>
+      <c r="AA22"/>
+      <c r="AB22"/>
+      <c r="AC22"/>
+      <c r="AD22"/>
+    </row>
+    <row r="23" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
         <v>5</v>
       </c>
@@ -1973,11 +2900,19 @@
       <c r="H23" t="str">
         <v>10.1.9</v>
       </c>
-      <c r="I23">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I23" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="J23">
+        <v>7.5</v>
+      </c>
+      <c r="Z23"/>
+      <c r="AA23"/>
+      <c r="AB23"/>
+      <c r="AC23"/>
+      <c r="AD23"/>
+    </row>
+    <row r="24" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
         <v>14</v>
       </c>
@@ -1987,11 +2922,19 @@
       <c r="H24" t="str">
         <v>10.1.8</v>
       </c>
-      <c r="I24">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I24" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="J24">
+        <v>7.5</v>
+      </c>
+      <c r="Z24"/>
+      <c r="AA24"/>
+      <c r="AB24"/>
+      <c r="AC24"/>
+      <c r="AD24"/>
+    </row>
+    <row r="25" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>16</v>
       </c>
@@ -2008,11 +2951,19 @@
       <c r="H25" t="str">
         <v>10.1.7</v>
       </c>
-      <c r="I25">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I25" s="6" t="s">
+        <v>398</v>
+      </c>
+      <c r="J25">
+        <v>7.5</v>
+      </c>
+      <c r="Z25"/>
+      <c r="AA25"/>
+      <c r="AB25"/>
+      <c r="AC25"/>
+      <c r="AD25"/>
+    </row>
+    <row r="26" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B26" t="s">
         <v>5</v>
       </c>
@@ -2022,11 +2973,19 @@
       <c r="H26" t="str">
         <v>10.1.6</v>
       </c>
-      <c r="I26">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I26" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="J26">
+        <v>7.5</v>
+      </c>
+      <c r="Z26"/>
+      <c r="AA26"/>
+      <c r="AB26"/>
+      <c r="AC26"/>
+      <c r="AD26"/>
+    </row>
+    <row r="27" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
         <v>14</v>
       </c>
@@ -2036,11 +2995,19 @@
       <c r="H27" t="str">
         <v>10.1.5</v>
       </c>
-      <c r="I27">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I27" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="J27">
+        <v>7.5</v>
+      </c>
+      <c r="Z27"/>
+      <c r="AA27"/>
+      <c r="AB27"/>
+      <c r="AC27"/>
+      <c r="AD27"/>
+    </row>
+    <row r="28" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>17</v>
       </c>
@@ -2057,11 +3024,19 @@
       <c r="H28" t="str">
         <v>10.1.4</v>
       </c>
-      <c r="I28">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I28" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="J28">
+        <v>7.5</v>
+      </c>
+      <c r="Z28"/>
+      <c r="AA28"/>
+      <c r="AB28"/>
+      <c r="AC28"/>
+      <c r="AD28"/>
+    </row>
+    <row r="29" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
         <v>5</v>
       </c>
@@ -2071,11 +3046,19 @@
       <c r="H29" t="str">
         <v>10.1.2</v>
       </c>
-      <c r="I29">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I29" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="J29">
+        <v>7.5</v>
+      </c>
+      <c r="Z29"/>
+      <c r="AA29"/>
+      <c r="AB29"/>
+      <c r="AC29"/>
+      <c r="AD29"/>
+    </row>
+    <row r="30" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B30" t="s">
         <v>14</v>
       </c>
@@ -2085,11 +3068,20 @@
       <c r="H30" t="str">
         <v>10.1.1</v>
       </c>
-      <c r="I30">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I30" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="J30">
+        <v>7.5</v>
+      </c>
+      <c r="Z30"/>
+      <c r="AA30"/>
+      <c r="AB30"/>
+      <c r="AC30"/>
+      <c r="AD30"/>
+      <c r="AE30"/>
+    </row>
+    <row r="31" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>18</v>
       </c>
@@ -2106,11 +3098,20 @@
       <c r="H31" t="str">
         <v>10.1.0</v>
       </c>
-      <c r="I31">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I31" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="J31">
+        <v>7.5</v>
+      </c>
+      <c r="Z31"/>
+      <c r="AA31"/>
+      <c r="AB31"/>
+      <c r="AC31"/>
+      <c r="AD31"/>
+      <c r="AE31"/>
+    </row>
+    <row r="32" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B32" t="s">
         <v>5</v>
       </c>
@@ -2120,11 +3121,20 @@
       <c r="H32" t="str">
         <v>10.0.27</v>
       </c>
-      <c r="I32">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I32" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="J32">
+        <v>7.5</v>
+      </c>
+      <c r="Z32"/>
+      <c r="AA32"/>
+      <c r="AB32"/>
+      <c r="AC32"/>
+      <c r="AD32"/>
+      <c r="AE32"/>
+    </row>
+    <row r="33" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B33" t="s">
         <v>14</v>
       </c>
@@ -2134,11 +3144,20 @@
       <c r="H33" t="str">
         <v>10.0.26</v>
       </c>
-      <c r="I33">
+      <c r="I33" s="6" t="s">
+        <v>420</v>
+      </c>
+      <c r="J33">
         <v>6.15</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z33"/>
+      <c r="AA33"/>
+      <c r="AB33"/>
+      <c r="AC33"/>
+      <c r="AD33"/>
+      <c r="AE33"/>
+    </row>
+    <row r="34" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B34" t="s">
         <v>19</v>
       </c>
@@ -2148,11 +3167,20 @@
       <c r="H34" t="str">
         <v>10.0.23</v>
       </c>
-      <c r="I34">
+      <c r="I34" s="6" t="s">
+        <v>421</v>
+      </c>
+      <c r="J34">
         <v>6.15</v>
       </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z34"/>
+      <c r="AA34"/>
+      <c r="AB34"/>
+      <c r="AC34"/>
+      <c r="AD34"/>
+      <c r="AE34"/>
+    </row>
+    <row r="35" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>20</v>
       </c>
@@ -2169,11 +3197,19 @@
       <c r="H35" t="str">
         <v>10.0.22</v>
       </c>
-      <c r="I35">
+      <c r="I35" s="6" t="s">
+        <v>422</v>
+      </c>
+      <c r="J35">
         <v>6.15</v>
       </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="AA35"/>
+      <c r="AB35"/>
+      <c r="AC35"/>
+      <c r="AD35"/>
+      <c r="AE35"/>
+    </row>
+    <row r="36" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B36" t="s">
         <v>5</v>
       </c>
@@ -2183,11 +3219,19 @@
       <c r="H36" t="str">
         <v>10.0.21</v>
       </c>
-      <c r="I36">
+      <c r="I36" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="J36">
         <v>6.15</v>
       </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="AA36"/>
+      <c r="AB36"/>
+      <c r="AC36"/>
+      <c r="AD36"/>
+      <c r="AE36"/>
+    </row>
+    <row r="37" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B37" t="s">
         <v>14</v>
       </c>
@@ -2197,11 +3241,19 @@
       <c r="H37" t="str">
         <v>10.0.20</v>
       </c>
-      <c r="I37">
+      <c r="I37" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="J37">
         <v>6.15</v>
       </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="AA37"/>
+      <c r="AB37"/>
+      <c r="AC37"/>
+      <c r="AD37"/>
+      <c r="AE37"/>
+    </row>
+    <row r="38" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B38" t="s">
         <v>19</v>
       </c>
@@ -2211,11 +3263,19 @@
       <c r="H38" t="str">
         <v>10.0.18</v>
       </c>
-      <c r="I38">
+      <c r="I38" s="6" t="s">
+        <v>409</v>
+      </c>
+      <c r="J38">
         <v>6.15</v>
       </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="AA38"/>
+      <c r="AB38"/>
+      <c r="AC38"/>
+      <c r="AD38"/>
+      <c r="AE38"/>
+    </row>
+    <row r="39" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>21</v>
       </c>
@@ -2232,11 +3292,19 @@
       <c r="H39" t="str">
         <v>10.0.17</v>
       </c>
-      <c r="I39">
+      <c r="I39" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="J39">
         <v>6.15</v>
       </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="AA39"/>
+      <c r="AB39"/>
+      <c r="AC39"/>
+      <c r="AD39"/>
+      <c r="AE39"/>
+    </row>
+    <row r="40" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B40" t="s">
         <v>5</v>
       </c>
@@ -2246,11 +3314,19 @@
       <c r="H40" t="str">
         <v>10.0.16</v>
       </c>
-      <c r="I40">
+      <c r="I40" s="6" t="s">
+        <v>411</v>
+      </c>
+      <c r="J40">
         <v>6.15</v>
       </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="AA40"/>
+      <c r="AB40"/>
+      <c r="AC40"/>
+      <c r="AD40"/>
+      <c r="AE40"/>
+    </row>
+    <row r="41" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B41" t="s">
         <v>14</v>
       </c>
@@ -2260,11 +3336,19 @@
       <c r="H41" t="str">
         <v>10.0.14</v>
       </c>
-      <c r="I41">
+      <c r="I41" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="J41">
         <v>6.15</v>
       </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="AA41"/>
+      <c r="AB41"/>
+      <c r="AC41"/>
+      <c r="AD41"/>
+      <c r="AE41"/>
+    </row>
+    <row r="42" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B42" t="s">
         <v>19</v>
       </c>
@@ -2274,11 +3358,19 @@
       <c r="H42" t="str">
         <v>10.0.13</v>
       </c>
-      <c r="I42">
+      <c r="I42" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="J42">
         <v>6.15</v>
       </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="AA42"/>
+      <c r="AB42"/>
+      <c r="AC42"/>
+      <c r="AD42"/>
+      <c r="AE42"/>
+    </row>
+    <row r="43" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>22</v>
       </c>
@@ -2295,11 +3387,19 @@
       <c r="H43" t="str">
         <v>10.0.12</v>
       </c>
-      <c r="I43">
+      <c r="I43" s="6" t="s">
+        <v>414</v>
+      </c>
+      <c r="J43">
         <v>6.15</v>
       </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="AA43"/>
+      <c r="AB43"/>
+      <c r="AC43"/>
+      <c r="AD43"/>
+      <c r="AE43"/>
+    </row>
+    <row r="44" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B44" t="s">
         <v>5</v>
       </c>
@@ -2309,11 +3409,19 @@
       <c r="H44" t="str">
         <v>10.0.11</v>
       </c>
-      <c r="I44">
+      <c r="I44" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="J44">
         <v>6.15</v>
       </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="AA44"/>
+      <c r="AB44"/>
+      <c r="AC44"/>
+      <c r="AD44"/>
+      <c r="AE44"/>
+    </row>
+    <row r="45" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B45" t="s">
         <v>14</v>
       </c>
@@ -2323,11 +3431,19 @@
       <c r="H45" t="str">
         <v>10.0.10</v>
       </c>
-      <c r="I45">
+      <c r="I45" s="6" t="s">
+        <v>423</v>
+      </c>
+      <c r="J45">
         <v>6.15</v>
       </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="AA45"/>
+      <c r="AB45"/>
+      <c r="AC45"/>
+      <c r="AD45"/>
+      <c r="AE45"/>
+    </row>
+    <row r="46" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B46" t="s">
         <v>19</v>
       </c>
@@ -2337,11 +3453,19 @@
       <c r="H46" t="str">
         <v>10.0.8</v>
       </c>
-      <c r="I46">
+      <c r="I46" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="J46">
         <v>6.15</v>
       </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="AA46"/>
+      <c r="AB46"/>
+      <c r="AC46"/>
+      <c r="AD46"/>
+      <c r="AE46"/>
+    </row>
+    <row r="47" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B47" t="s">
         <v>23</v>
       </c>
@@ -2351,11 +3475,19 @@
       <c r="H47" t="str">
         <v>10.0.7</v>
       </c>
-      <c r="I47">
+      <c r="I47" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="J47">
         <v>6.15</v>
       </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="AA47"/>
+      <c r="AB47"/>
+      <c r="AC47"/>
+      <c r="AD47"/>
+      <c r="AE47"/>
+    </row>
+    <row r="48" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>24</v>
       </c>
@@ -2372,11 +3504,19 @@
       <c r="H48" t="str">
         <v>10.0.6</v>
       </c>
-      <c r="I48">
+      <c r="I48" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="J48">
         <v>6.15</v>
       </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="AA48"/>
+      <c r="AB48"/>
+      <c r="AC48"/>
+      <c r="AD48"/>
+      <c r="AE48"/>
+    </row>
+    <row r="49" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B49" t="s">
         <v>5</v>
       </c>
@@ -2386,11 +3526,19 @@
       <c r="H49" t="str">
         <v>10.0.5</v>
       </c>
-      <c r="I49">
+      <c r="I49" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="J49">
         <v>6.15</v>
       </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="AA49"/>
+      <c r="AB49"/>
+      <c r="AC49"/>
+      <c r="AD49"/>
+      <c r="AE49"/>
+    </row>
+    <row r="50" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B50" t="s">
         <v>14</v>
       </c>
@@ -2400,11 +3548,19 @@
       <c r="H50" t="str">
         <v>10.0.4</v>
       </c>
-      <c r="I50">
+      <c r="I50" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="J50">
         <v>6.15</v>
       </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="AA50"/>
+      <c r="AB50"/>
+      <c r="AC50"/>
+      <c r="AD50"/>
+      <c r="AE50"/>
+    </row>
+    <row r="51" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B51" t="s">
         <v>19</v>
       </c>
@@ -2414,11 +3570,19 @@
       <c r="H51" t="str">
         <v>10.0.2</v>
       </c>
-      <c r="I51">
+      <c r="I51" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="J51">
         <v>6.15</v>
       </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="AA51"/>
+      <c r="AB51"/>
+      <c r="AC51"/>
+      <c r="AD51"/>
+      <c r="AE51"/>
+    </row>
+    <row r="52" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B52" t="s">
         <v>23</v>
       </c>
@@ -2428,11 +3592,19 @@
       <c r="H52" t="str">
         <v>10.0.0</v>
       </c>
-      <c r="I52">
+      <c r="I52" s="6" t="s">
+        <v>429</v>
+      </c>
+      <c r="J52">
         <v>7.25</v>
       </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="AA52"/>
+      <c r="AB52"/>
+      <c r="AC52"/>
+      <c r="AD52"/>
+      <c r="AE52"/>
+    </row>
+    <row r="53" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>25</v>
       </c>
@@ -2449,11 +3621,19 @@
       <c r="H53" t="str">
         <v>9.0.97</v>
       </c>
-      <c r="I53">
+      <c r="I53" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="J53">
         <v>8.1</v>
       </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="AA53"/>
+      <c r="AB53"/>
+      <c r="AC53"/>
+      <c r="AD53"/>
+      <c r="AE53"/>
+    </row>
+    <row r="54" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B54" t="s">
         <v>5</v>
       </c>
@@ -2463,11 +3643,19 @@
       <c r="H54" t="str">
         <v>9.0.96</v>
       </c>
-      <c r="I54">
+      <c r="I54" s="6" t="s">
+        <v>437</v>
+      </c>
+      <c r="J54">
         <v>8.1</v>
       </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="AA54"/>
+      <c r="AB54"/>
+      <c r="AC54"/>
+      <c r="AD54"/>
+      <c r="AE54"/>
+    </row>
+    <row r="55" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B55" t="s">
         <v>14</v>
       </c>
@@ -2477,11 +3665,19 @@
       <c r="H55" t="str">
         <v>9.0.95</v>
       </c>
-      <c r="I55">
+      <c r="I55" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="J55">
         <v>8.1</v>
       </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="AA55"/>
+      <c r="AB55"/>
+      <c r="AC55"/>
+      <c r="AD55"/>
+      <c r="AE55"/>
+    </row>
+    <row r="56" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B56" t="s">
         <v>19</v>
       </c>
@@ -2491,11 +3687,19 @@
       <c r="H56" t="str">
         <v>9.0.94</v>
       </c>
-      <c r="I56">
+      <c r="I56" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="J56">
         <v>8.1</v>
       </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="AA56"/>
+      <c r="AB56"/>
+      <c r="AC56"/>
+      <c r="AD56"/>
+      <c r="AE56"/>
+    </row>
+    <row r="57" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B57" t="s">
         <v>23</v>
       </c>
@@ -2505,11 +3709,19 @@
       <c r="H57" t="str">
         <v>9.0.93</v>
       </c>
-      <c r="I57">
+      <c r="I57" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="J57">
         <v>8.1</v>
       </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="AA57"/>
+      <c r="AB57"/>
+      <c r="AC57"/>
+      <c r="AD57"/>
+      <c r="AE57"/>
+    </row>
+    <row r="58" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B58" t="s">
         <v>26</v>
       </c>
@@ -2519,11 +3731,19 @@
       <c r="H58" t="str">
         <v>9.0.91</v>
       </c>
-      <c r="I58">
+      <c r="I58" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="J58">
         <v>8.1</v>
       </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="AA58"/>
+      <c r="AB58"/>
+      <c r="AC58"/>
+      <c r="AD58"/>
+      <c r="AE58"/>
+    </row>
+    <row r="59" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B59" t="s">
         <v>27</v>
       </c>
@@ -2533,11 +3753,19 @@
       <c r="H59" t="str">
         <v>9.0.90</v>
       </c>
-      <c r="I59">
+      <c r="I59" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="J59">
         <v>8.1</v>
       </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="AA59"/>
+      <c r="AB59"/>
+      <c r="AC59"/>
+      <c r="AD59"/>
+      <c r="AE59"/>
+    </row>
+    <row r="60" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B60" t="s">
         <v>28</v>
       </c>
@@ -2547,11 +3775,19 @@
       <c r="H60" t="str">
         <v>9.0.89</v>
       </c>
-      <c r="I60">
+      <c r="I60" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="J60">
         <v>8.1</v>
       </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="AA60"/>
+      <c r="AB60"/>
+      <c r="AC60"/>
+      <c r="AD60"/>
+      <c r="AE60"/>
+    </row>
+    <row r="61" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>29</v>
       </c>
@@ -2568,11 +3804,19 @@
       <c r="H61" t="str">
         <v>9.0.88</v>
       </c>
-      <c r="I61">
+      <c r="I61" s="6" t="s">
+        <v>440</v>
+      </c>
+      <c r="J61">
         <v>8.1</v>
       </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="AA61"/>
+      <c r="AB61"/>
+      <c r="AC61"/>
+      <c r="AD61"/>
+      <c r="AE61"/>
+    </row>
+    <row r="62" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B62" t="s">
         <v>5</v>
       </c>
@@ -2582,11 +3826,19 @@
       <c r="H62" t="str">
         <v>9.0.87</v>
       </c>
-      <c r="I62">
+      <c r="I62" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="J62">
         <v>8.1</v>
       </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="AA62"/>
+      <c r="AB62"/>
+      <c r="AC62"/>
+      <c r="AD62"/>
+      <c r="AE62"/>
+    </row>
+    <row r="63" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B63" t="s">
         <v>14</v>
       </c>
@@ -2596,11 +3848,19 @@
       <c r="H63" t="str">
         <v>9.0.86</v>
       </c>
-      <c r="I63">
+      <c r="I63" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="J63">
         <v>8.1</v>
       </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="AA63"/>
+      <c r="AB63"/>
+      <c r="AC63"/>
+      <c r="AD63"/>
+      <c r="AE63"/>
+    </row>
+    <row r="64" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B64" t="s">
         <v>19</v>
       </c>
@@ -2610,11 +3870,19 @@
       <c r="H64" t="str">
         <v>9.0.85</v>
       </c>
-      <c r="I64">
+      <c r="I64" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="J64">
         <v>7.8</v>
       </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="AA64"/>
+      <c r="AB64"/>
+      <c r="AC64"/>
+      <c r="AD64"/>
+      <c r="AE64"/>
+    </row>
+    <row r="65" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B65" t="s">
         <v>23</v>
       </c>
@@ -2624,11 +3892,19 @@
       <c r="H65" t="str">
         <v>9.0.84</v>
       </c>
-      <c r="I65">
+      <c r="I65" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="J65">
         <v>7.8</v>
       </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="AA65"/>
+      <c r="AB65"/>
+      <c r="AC65"/>
+      <c r="AD65"/>
+      <c r="AE65"/>
+    </row>
+    <row r="66" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B66" t="s">
         <v>26</v>
       </c>
@@ -2638,11 +3914,19 @@
       <c r="H66" t="str">
         <v>9.0.83</v>
       </c>
-      <c r="I66">
+      <c r="I66" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="J66">
         <v>7.8</v>
       </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="AA66"/>
+      <c r="AB66"/>
+      <c r="AC66"/>
+      <c r="AD66"/>
+      <c r="AE66"/>
+    </row>
+    <row r="67" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B67" t="s">
         <v>27</v>
       </c>
@@ -2652,11 +3936,19 @@
       <c r="H67" t="str">
         <v>9.0.82</v>
       </c>
-      <c r="I67">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I67" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="J67">
+        <v>7.5</v>
+      </c>
+      <c r="AA67"/>
+      <c r="AB67"/>
+      <c r="AC67"/>
+      <c r="AD67"/>
+      <c r="AE67"/>
+    </row>
+    <row r="68" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B68" t="s">
         <v>28</v>
       </c>
@@ -2666,11 +3958,19 @@
       <c r="H68" t="str">
         <v>9.0.81</v>
       </c>
-      <c r="I68">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I68" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="J68">
+        <v>7.5</v>
+      </c>
+      <c r="AA68"/>
+      <c r="AB68"/>
+      <c r="AC68"/>
+      <c r="AD68"/>
+      <c r="AE68"/>
+    </row>
+    <row r="69" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B69" t="s">
         <v>30</v>
       </c>
@@ -2680,11 +3980,19 @@
       <c r="H69" t="str">
         <v>9.0.80</v>
       </c>
-      <c r="I69">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I69" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="J69">
+        <v>7.5</v>
+      </c>
+      <c r="AA69"/>
+      <c r="AB69"/>
+      <c r="AC69"/>
+      <c r="AD69"/>
+      <c r="AE69"/>
+    </row>
+    <row r="70" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>31</v>
       </c>
@@ -2701,11 +4009,19 @@
       <c r="H70" t="str">
         <v>9.0.79</v>
       </c>
-      <c r="I70">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I70" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="J70">
+        <v>7.5</v>
+      </c>
+      <c r="AA70"/>
+      <c r="AB70"/>
+      <c r="AC70"/>
+      <c r="AD70"/>
+      <c r="AE70"/>
+    </row>
+    <row r="71" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B71" t="s">
         <v>5</v>
       </c>
@@ -2715,11 +4031,19 @@
       <c r="H71" t="str">
         <v>9.0.78</v>
       </c>
-      <c r="I71">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I71" s="6" t="s">
+        <v>443</v>
+      </c>
+      <c r="J71">
+        <v>7.5</v>
+      </c>
+      <c r="AA71"/>
+      <c r="AB71"/>
+      <c r="AC71"/>
+      <c r="AD71"/>
+      <c r="AE71"/>
+    </row>
+    <row r="72" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B72" t="s">
         <v>14</v>
       </c>
@@ -2729,11 +4053,19 @@
       <c r="H72" t="str">
         <v>9.0.77</v>
       </c>
-      <c r="I72">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I72" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="J72">
+        <v>7.5</v>
+      </c>
+      <c r="AA72"/>
+      <c r="AB72"/>
+      <c r="AC72"/>
+      <c r="AD72"/>
+      <c r="AE72"/>
+    </row>
+    <row r="73" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B73" t="s">
         <v>19</v>
       </c>
@@ -2743,11 +4075,19 @@
       <c r="H73" t="str">
         <v>9.0.76</v>
       </c>
-      <c r="I73">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I73" s="6" t="s">
+        <v>444</v>
+      </c>
+      <c r="J73">
+        <v>7.5</v>
+      </c>
+      <c r="AA73"/>
+      <c r="AB73"/>
+      <c r="AC73"/>
+      <c r="AD73"/>
+      <c r="AE73"/>
+    </row>
+    <row r="74" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B74" t="s">
         <v>23</v>
       </c>
@@ -2757,11 +4097,19 @@
       <c r="H74" t="str">
         <v>9.0.75</v>
       </c>
-      <c r="I74">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I74" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="J74">
+        <v>7.5</v>
+      </c>
+      <c r="AA74"/>
+      <c r="AB74"/>
+      <c r="AC74"/>
+      <c r="AD74"/>
+      <c r="AE74"/>
+    </row>
+    <row r="75" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B75" t="s">
         <v>26</v>
       </c>
@@ -2771,11 +4119,19 @@
       <c r="H75" t="str">
         <v>9.0.74</v>
       </c>
-      <c r="I75">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I75" s="6" t="s">
+        <v>446</v>
+      </c>
+      <c r="J75">
+        <v>7.5</v>
+      </c>
+      <c r="AA75"/>
+      <c r="AB75"/>
+      <c r="AC75"/>
+      <c r="AD75"/>
+      <c r="AE75"/>
+    </row>
+    <row r="76" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B76" t="s">
         <v>27</v>
       </c>
@@ -2785,11 +4141,19 @@
       <c r="H76" t="str">
         <v>9.0.73</v>
       </c>
-      <c r="I76">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I76" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="J76">
+        <v>7.5</v>
+      </c>
+      <c r="AA76"/>
+      <c r="AB76"/>
+      <c r="AC76"/>
+      <c r="AD76"/>
+      <c r="AE76"/>
+    </row>
+    <row r="77" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B77" t="s">
         <v>28</v>
       </c>
@@ -2799,11 +4163,19 @@
       <c r="H77" t="str">
         <v>9.0.72</v>
       </c>
-      <c r="I77">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I77" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="J77">
+        <v>7.5</v>
+      </c>
+      <c r="AA77"/>
+      <c r="AB77"/>
+      <c r="AC77"/>
+      <c r="AD77"/>
+      <c r="AE77"/>
+    </row>
+    <row r="78" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B78" t="s">
         <v>30</v>
       </c>
@@ -2813,11 +4185,20 @@
       <c r="H78" t="str">
         <v>9.0.71</v>
       </c>
-      <c r="I78">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I78" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="J78">
+        <v>7.5</v>
+      </c>
+      <c r="Z78"/>
+      <c r="AA78"/>
+      <c r="AB78"/>
+      <c r="AC78"/>
+      <c r="AD78"/>
+      <c r="AE78"/>
+    </row>
+    <row r="79" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>32</v>
       </c>
@@ -2834,11 +4215,20 @@
       <c r="H79" t="str">
         <v>9.0.70</v>
       </c>
-      <c r="I79">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I79" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="J79">
+        <v>7.5</v>
+      </c>
+      <c r="Z79"/>
+      <c r="AA79"/>
+      <c r="AB79"/>
+      <c r="AC79"/>
+      <c r="AD79"/>
+      <c r="AE79"/>
+    </row>
+    <row r="80" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B80" t="s">
         <v>5</v>
       </c>
@@ -2848,11 +4238,20 @@
       <c r="H80" t="str">
         <v>9.0.69</v>
       </c>
-      <c r="I80">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I80" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="J80">
+        <v>7.5</v>
+      </c>
+      <c r="Z80"/>
+      <c r="AA80"/>
+      <c r="AB80"/>
+      <c r="AC80"/>
+      <c r="AD80"/>
+      <c r="AE80"/>
+    </row>
+    <row r="81" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B81" t="s">
         <v>14</v>
       </c>
@@ -2862,11 +4261,20 @@
       <c r="H81" t="str">
         <v>9.0.68</v>
       </c>
-      <c r="I81">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I81" s="6" t="s">
+        <v>448</v>
+      </c>
+      <c r="J81">
+        <v>7.5</v>
+      </c>
+      <c r="Z81"/>
+      <c r="AA81"/>
+      <c r="AB81"/>
+      <c r="AC81"/>
+      <c r="AD81"/>
+      <c r="AE81"/>
+    </row>
+    <row r="82" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B82" t="s">
         <v>19</v>
       </c>
@@ -2876,11 +4284,20 @@
       <c r="H82" t="str">
         <v>9.0.67</v>
       </c>
-      <c r="I82">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I82" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="J82">
+        <v>7.5</v>
+      </c>
+      <c r="Z82"/>
+      <c r="AA82"/>
+      <c r="AB82"/>
+      <c r="AC82"/>
+      <c r="AD82"/>
+      <c r="AE82"/>
+    </row>
+    <row r="83" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B83" t="s">
         <v>23</v>
       </c>
@@ -2890,11 +4307,20 @@
       <c r="H83" t="str">
         <v>9.0.65</v>
       </c>
-      <c r="I83">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I83" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="J83">
+        <v>7.5</v>
+      </c>
+      <c r="Z83"/>
+      <c r="AA83"/>
+      <c r="AB83"/>
+      <c r="AC83"/>
+      <c r="AD83"/>
+      <c r="AE83"/>
+    </row>
+    <row r="84" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B84" t="s">
         <v>26</v>
       </c>
@@ -2904,11 +4330,20 @@
       <c r="H84" t="str">
         <v>9.0.64</v>
       </c>
-      <c r="I84">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I84" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="J84">
+        <v>7.5</v>
+      </c>
+      <c r="Z84"/>
+      <c r="AA84"/>
+      <c r="AB84"/>
+      <c r="AC84"/>
+      <c r="AD84"/>
+      <c r="AE84"/>
+    </row>
+    <row r="85" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B85" t="s">
         <v>27</v>
       </c>
@@ -2918,11 +4353,20 @@
       <c r="H85" t="str">
         <v>9.0.63</v>
       </c>
-      <c r="I85">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I85" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="J85">
+        <v>7.5</v>
+      </c>
+      <c r="Z85"/>
+      <c r="AA85"/>
+      <c r="AB85"/>
+      <c r="AC85"/>
+      <c r="AD85"/>
+      <c r="AE85"/>
+    </row>
+    <row r="86" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B86" t="s">
         <v>28</v>
       </c>
@@ -2932,11 +4376,20 @@
       <c r="H86" t="str">
         <v>9.0.62</v>
       </c>
-      <c r="I86">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I86" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="J86">
+        <v>7.5</v>
+      </c>
+      <c r="Z86"/>
+      <c r="AA86"/>
+      <c r="AB86"/>
+      <c r="AC86"/>
+      <c r="AD86"/>
+      <c r="AE86"/>
+    </row>
+    <row r="87" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B87" t="s">
         <v>30</v>
       </c>
@@ -2946,11 +4399,20 @@
       <c r="H87" t="str">
         <v>9.0.60</v>
       </c>
-      <c r="I87">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I87" s="6" t="s">
+        <v>409</v>
+      </c>
+      <c r="J87">
+        <v>7.5</v>
+      </c>
+      <c r="Z87"/>
+      <c r="AA87"/>
+      <c r="AB87"/>
+      <c r="AC87"/>
+      <c r="AD87"/>
+      <c r="AE87"/>
+    </row>
+    <row r="88" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>33</v>
       </c>
@@ -2967,11 +4429,20 @@
       <c r="H88" t="str">
         <v>9.0.59</v>
       </c>
-      <c r="I88">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I88" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="J88">
+        <v>7.5</v>
+      </c>
+      <c r="Z88"/>
+      <c r="AA88"/>
+      <c r="AB88"/>
+      <c r="AC88"/>
+      <c r="AD88"/>
+      <c r="AE88"/>
+    </row>
+    <row r="89" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B89" t="s">
         <v>5</v>
       </c>
@@ -2981,11 +4452,20 @@
       <c r="H89" t="str">
         <v>9.0.58</v>
       </c>
-      <c r="I89">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I89" s="6" t="s">
+        <v>411</v>
+      </c>
+      <c r="J89">
+        <v>7.5</v>
+      </c>
+      <c r="Z89"/>
+      <c r="AA89"/>
+      <c r="AB89"/>
+      <c r="AC89"/>
+      <c r="AD89"/>
+      <c r="AE89"/>
+    </row>
+    <row r="90" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B90" t="s">
         <v>14</v>
       </c>
@@ -2995,11 +4475,20 @@
       <c r="H90" t="str">
         <v>9.0.56</v>
       </c>
-      <c r="I90">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I90" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="J90">
+        <v>7.5</v>
+      </c>
+      <c r="Z90"/>
+      <c r="AA90"/>
+      <c r="AB90"/>
+      <c r="AC90"/>
+      <c r="AD90"/>
+      <c r="AE90"/>
+    </row>
+    <row r="91" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B91" t="s">
         <v>19</v>
       </c>
@@ -3009,11 +4498,20 @@
       <c r="H91" t="str">
         <v>9.0.55</v>
       </c>
-      <c r="I91">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I91" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="J91">
+        <v>7.5</v>
+      </c>
+      <c r="Z91"/>
+      <c r="AA91"/>
+      <c r="AB91"/>
+      <c r="AC91"/>
+      <c r="AD91"/>
+      <c r="AE91"/>
+    </row>
+    <row r="92" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B92" t="s">
         <v>23</v>
       </c>
@@ -3023,11 +4521,20 @@
       <c r="H92" t="str">
         <v>9.0.54</v>
       </c>
-      <c r="I92">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I92" s="6" t="s">
+        <v>449</v>
+      </c>
+      <c r="J92">
+        <v>7.5</v>
+      </c>
+      <c r="Z92"/>
+      <c r="AA92"/>
+      <c r="AB92"/>
+      <c r="AC92"/>
+      <c r="AD92"/>
+      <c r="AE92"/>
+    </row>
+    <row r="93" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B93" t="s">
         <v>26</v>
       </c>
@@ -3037,11 +4544,20 @@
       <c r="H93" t="str">
         <v>9.0.53</v>
       </c>
-      <c r="I93">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I93" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="J93">
+        <v>7.5</v>
+      </c>
+      <c r="Z93"/>
+      <c r="AA93"/>
+      <c r="AB93"/>
+      <c r="AC93"/>
+      <c r="AD93"/>
+      <c r="AE93"/>
+    </row>
+    <row r="94" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B94" t="s">
         <v>27</v>
       </c>
@@ -3051,11 +4567,20 @@
       <c r="H94" t="str">
         <v>9.0.52</v>
       </c>
-      <c r="I94">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I94" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="J94">
+        <v>7.5</v>
+      </c>
+      <c r="Z94"/>
+      <c r="AA94"/>
+      <c r="AB94"/>
+      <c r="AC94"/>
+      <c r="AD94"/>
+      <c r="AE94"/>
+    </row>
+    <row r="95" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B95" t="s">
         <v>28</v>
       </c>
@@ -3065,11 +4590,20 @@
       <c r="H95" t="str">
         <v>9.0.50</v>
       </c>
-      <c r="I95">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I95" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="J95">
+        <v>7.5</v>
+      </c>
+      <c r="Z95"/>
+      <c r="AA95"/>
+      <c r="AB95"/>
+      <c r="AC95"/>
+      <c r="AD95"/>
+      <c r="AE95"/>
+    </row>
+    <row r="96" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B96" t="s">
         <v>30</v>
       </c>
@@ -3079,11 +4613,20 @@
       <c r="H96" t="str">
         <v>9.0.48</v>
       </c>
-      <c r="I96">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I96" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="J96">
+        <v>7.5</v>
+      </c>
+      <c r="Z96"/>
+      <c r="AA96"/>
+      <c r="AB96"/>
+      <c r="AC96"/>
+      <c r="AD96"/>
+      <c r="AE96"/>
+    </row>
+    <row r="97" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>34</v>
       </c>
@@ -3100,11 +4643,20 @@
       <c r="H97" t="str">
         <v>9.0.46</v>
       </c>
-      <c r="I97">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I97" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="J97">
+        <v>7.5</v>
+      </c>
+      <c r="Z97"/>
+      <c r="AA97"/>
+      <c r="AB97"/>
+      <c r="AC97"/>
+      <c r="AD97"/>
+      <c r="AE97"/>
+    </row>
+    <row r="98" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B98" t="s">
         <v>5</v>
       </c>
@@ -3114,11 +4666,20 @@
       <c r="H98" t="str">
         <v>9.0.45</v>
       </c>
-      <c r="I98">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I98" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="J98">
+        <v>7.5</v>
+      </c>
+      <c r="Z98"/>
+      <c r="AA98"/>
+      <c r="AB98"/>
+      <c r="AC98"/>
+      <c r="AD98"/>
+      <c r="AE98"/>
+    </row>
+    <row r="99" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B99" t="s">
         <v>14</v>
       </c>
@@ -3128,11 +4689,20 @@
       <c r="H99" t="str">
         <v>9.0.44</v>
       </c>
-      <c r="I99">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I99" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="J99">
+        <v>7.5</v>
+      </c>
+      <c r="Z99"/>
+      <c r="AA99"/>
+      <c r="AB99"/>
+      <c r="AC99"/>
+      <c r="AD99"/>
+      <c r="AE99"/>
+    </row>
+    <row r="100" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B100" t="s">
         <v>19</v>
       </c>
@@ -3142,11 +4712,20 @@
       <c r="H100" t="str">
         <v>9.0.43</v>
       </c>
-      <c r="I100">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I100" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="J100">
+        <v>7.5</v>
+      </c>
+      <c r="Z100"/>
+      <c r="AA100"/>
+      <c r="AB100"/>
+      <c r="AC100"/>
+      <c r="AD100"/>
+      <c r="AE100"/>
+    </row>
+    <row r="101" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B101" t="s">
         <v>23</v>
       </c>
@@ -3156,11 +4735,20 @@
       <c r="H101" t="str">
         <v>9.0.41</v>
       </c>
-      <c r="I101">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I101" s="6" t="s">
+        <v>429</v>
+      </c>
+      <c r="J101">
+        <v>7.5</v>
+      </c>
+      <c r="Z101"/>
+      <c r="AA101"/>
+      <c r="AB101"/>
+      <c r="AC101"/>
+      <c r="AD101"/>
+      <c r="AE101"/>
+    </row>
+    <row r="102" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B102" t="s">
         <v>26</v>
       </c>
@@ -3170,11 +4758,20 @@
       <c r="H102" t="str">
         <v>9.0.40</v>
       </c>
-      <c r="I102">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I102" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="J102">
+        <v>7.5</v>
+      </c>
+      <c r="Z102"/>
+      <c r="AA102"/>
+      <c r="AB102"/>
+      <c r="AC102"/>
+      <c r="AD102"/>
+      <c r="AE102"/>
+    </row>
+    <row r="103" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B103" t="s">
         <v>27</v>
       </c>
@@ -3184,11 +4781,20 @@
       <c r="H103" t="str">
         <v>9.0.39</v>
       </c>
-      <c r="I103">
+      <c r="I103" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="J103">
         <v>7.25</v>
       </c>
-    </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z103"/>
+      <c r="AA103"/>
+      <c r="AB103"/>
+      <c r="AC103"/>
+      <c r="AD103"/>
+      <c r="AE103"/>
+    </row>
+    <row r="104" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B104" t="s">
         <v>28</v>
       </c>
@@ -3198,11 +4804,20 @@
       <c r="H104" t="str">
         <v>9.0.38</v>
       </c>
-      <c r="I104">
+      <c r="I104" s="6" t="s">
+        <v>450</v>
+      </c>
+      <c r="J104">
         <v>7.25</v>
       </c>
-    </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z104"/>
+      <c r="AA104"/>
+      <c r="AB104"/>
+      <c r="AC104"/>
+      <c r="AD104"/>
+      <c r="AE104"/>
+    </row>
+    <row r="105" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B105" t="s">
         <v>30</v>
       </c>
@@ -3212,11 +4827,20 @@
       <c r="H105" t="str">
         <v>9.0.37</v>
       </c>
-      <c r="I105">
+      <c r="I105" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="J105">
         <v>7.25</v>
       </c>
-    </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z105"/>
+      <c r="AA105"/>
+      <c r="AB105"/>
+      <c r="AC105"/>
+      <c r="AD105"/>
+      <c r="AE105"/>
+    </row>
+    <row r="106" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B106" t="s">
         <v>35</v>
       </c>
@@ -3226,11 +4850,20 @@
       <c r="H106" t="str">
         <v>9.0.36</v>
       </c>
-      <c r="I106">
+      <c r="I106" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="J106">
         <v>7.25</v>
       </c>
-    </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z106"/>
+      <c r="AA106"/>
+      <c r="AB106"/>
+      <c r="AC106"/>
+      <c r="AD106"/>
+      <c r="AE106"/>
+    </row>
+    <row r="107" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>36</v>
       </c>
@@ -3247,11 +4880,20 @@
       <c r="H107" t="str">
         <v>9.0.35</v>
       </c>
-      <c r="I107">
+      <c r="I107" s="6" t="s">
+        <v>434</v>
+      </c>
+      <c r="J107">
         <v>7.25</v>
       </c>
-    </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z107"/>
+      <c r="AA107"/>
+      <c r="AB107"/>
+      <c r="AC107"/>
+      <c r="AD107"/>
+      <c r="AE107"/>
+    </row>
+    <row r="108" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B108" t="s">
         <v>5</v>
       </c>
@@ -3261,11 +4903,20 @@
       <c r="H108" t="str">
         <v>9.0.34</v>
       </c>
-      <c r="I108">
+      <c r="I108" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="J108">
         <v>7.25</v>
       </c>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z108"/>
+      <c r="AA108"/>
+      <c r="AB108"/>
+      <c r="AC108"/>
+      <c r="AD108"/>
+      <c r="AE108"/>
+    </row>
+    <row r="109" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B109" t="s">
         <v>14</v>
       </c>
@@ -3275,11 +4926,20 @@
       <c r="H109" t="str">
         <v>9.0.33</v>
       </c>
-      <c r="I109">
+      <c r="I109" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="J109">
         <v>7.25</v>
       </c>
-    </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z109"/>
+      <c r="AA109"/>
+      <c r="AB109"/>
+      <c r="AC109"/>
+      <c r="AD109"/>
+      <c r="AE109"/>
+    </row>
+    <row r="110" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B110" t="s">
         <v>19</v>
       </c>
@@ -3289,11 +4949,20 @@
       <c r="H110" t="str">
         <v>9.0.31</v>
       </c>
-      <c r="I110">
+      <c r="I110" s="6" t="s">
+        <v>451</v>
+      </c>
+      <c r="J110">
         <v>7.25</v>
       </c>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z110"/>
+      <c r="AA110"/>
+      <c r="AB110"/>
+      <c r="AC110"/>
+      <c r="AD110"/>
+      <c r="AE110"/>
+    </row>
+    <row r="111" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B111" t="s">
         <v>23</v>
       </c>
@@ -3303,11 +4972,20 @@
       <c r="H111" t="str">
         <v>9.0.30</v>
       </c>
-      <c r="I111">
+      <c r="I111" s="6" t="s">
+        <v>452</v>
+      </c>
+      <c r="J111">
         <v>7</v>
       </c>
-    </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z111"/>
+      <c r="AA111"/>
+      <c r="AB111"/>
+      <c r="AC111"/>
+      <c r="AD111"/>
+      <c r="AE111"/>
+    </row>
+    <row r="112" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B112" t="s">
         <v>26</v>
       </c>
@@ -3317,11 +4995,20 @@
       <c r="H112" t="str">
         <v>9.0.29</v>
       </c>
-      <c r="I112">
+      <c r="I112" s="6" t="s">
+        <v>453</v>
+      </c>
+      <c r="J112">
         <v>7.25</v>
       </c>
-    </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z112"/>
+      <c r="AA112"/>
+      <c r="AB112"/>
+      <c r="AC112"/>
+      <c r="AD112"/>
+      <c r="AE112"/>
+    </row>
+    <row r="113" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B113" t="s">
         <v>27</v>
       </c>
@@ -3331,11 +5018,20 @@
       <c r="H113" t="str">
         <v>9.0.27</v>
       </c>
-      <c r="I113">
+      <c r="I113" s="6" t="s">
+        <v>454</v>
+      </c>
+      <c r="J113">
         <v>7.45</v>
       </c>
-    </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z113"/>
+      <c r="AA113"/>
+      <c r="AB113"/>
+      <c r="AC113"/>
+      <c r="AD113"/>
+      <c r="AE113"/>
+    </row>
+    <row r="114" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B114" t="s">
         <v>28</v>
       </c>
@@ -3345,11 +5041,20 @@
       <c r="H114" t="str">
         <v>9.0.26</v>
       </c>
-      <c r="I114">
+      <c r="I114" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="J114">
         <v>7.45</v>
       </c>
-    </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z114"/>
+      <c r="AA114"/>
+      <c r="AB114"/>
+      <c r="AC114"/>
+      <c r="AD114"/>
+      <c r="AE114"/>
+    </row>
+    <row r="115" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B115" t="s">
         <v>30</v>
       </c>
@@ -3359,11 +5064,20 @@
       <c r="H115" t="str">
         <v>9.0.24</v>
       </c>
-      <c r="I115">
+      <c r="I115" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="J115">
         <v>7.45</v>
       </c>
-    </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z115"/>
+      <c r="AA115"/>
+      <c r="AB115"/>
+      <c r="AC115"/>
+      <c r="AD115"/>
+      <c r="AE115"/>
+    </row>
+    <row r="116" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B116" t="s">
         <v>37</v>
       </c>
@@ -3373,11 +5087,20 @@
       <c r="H116" t="str">
         <v>9.0.22</v>
       </c>
-      <c r="I116">
+      <c r="I116" s="6" t="s">
+        <v>457</v>
+      </c>
+      <c r="J116">
         <v>7.45</v>
       </c>
-    </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z116"/>
+      <c r="AA116"/>
+      <c r="AB116"/>
+      <c r="AC116"/>
+      <c r="AD116"/>
+      <c r="AE116"/>
+    </row>
+    <row r="117" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>38</v>
       </c>
@@ -3394,11 +5117,20 @@
       <c r="H117" t="str">
         <v>9.0.21</v>
       </c>
-      <c r="I117">
+      <c r="I117" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="J117">
         <v>7.45</v>
       </c>
-    </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z117"/>
+      <c r="AA117"/>
+      <c r="AB117"/>
+      <c r="AC117"/>
+      <c r="AD117"/>
+      <c r="AE117"/>
+    </row>
+    <row r="118" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B118" t="s">
         <v>5</v>
       </c>
@@ -3408,11 +5140,20 @@
       <c r="H118" t="str">
         <v>9.0.20</v>
       </c>
-      <c r="I118">
+      <c r="I118" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="J118">
         <v>7.45</v>
       </c>
-    </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z118"/>
+      <c r="AA118"/>
+      <c r="AB118"/>
+      <c r="AC118"/>
+      <c r="AD118"/>
+      <c r="AE118"/>
+    </row>
+    <row r="119" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B119" t="s">
         <v>14</v>
       </c>
@@ -3422,11 +5163,20 @@
       <c r="H119" t="str">
         <v>9.0.19</v>
       </c>
-      <c r="I119">
+      <c r="I119" s="6" t="s">
+        <v>460</v>
+      </c>
+      <c r="J119">
         <v>7.4</v>
       </c>
-    </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z119"/>
+      <c r="AA119"/>
+      <c r="AB119"/>
+      <c r="AC119"/>
+      <c r="AD119"/>
+      <c r="AE119"/>
+    </row>
+    <row r="120" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B120" t="s">
         <v>19</v>
       </c>
@@ -3436,11 +5186,20 @@
       <c r="H120" t="str">
         <v>9.0.17</v>
       </c>
-      <c r="I120">
+      <c r="I120" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="J120">
         <v>7.4</v>
       </c>
-    </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z120"/>
+      <c r="AA120"/>
+      <c r="AB120"/>
+      <c r="AC120"/>
+      <c r="AD120"/>
+      <c r="AE120"/>
+    </row>
+    <row r="121" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B121" t="s">
         <v>23</v>
       </c>
@@ -3450,11 +5209,20 @@
       <c r="H121" t="str">
         <v>9.0.16</v>
       </c>
-      <c r="I121">
+      <c r="I121" s="6" t="s">
+        <v>462</v>
+      </c>
+      <c r="J121">
         <v>7</v>
       </c>
-    </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z121"/>
+      <c r="AA121"/>
+      <c r="AB121"/>
+      <c r="AC121"/>
+      <c r="AD121"/>
+      <c r="AE121"/>
+    </row>
+    <row r="122" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B122" t="s">
         <v>26</v>
       </c>
@@ -3464,11 +5232,20 @@
       <c r="H122" t="str">
         <v>9.0.14</v>
       </c>
-      <c r="I122">
+      <c r="I122" s="6" t="s">
+        <v>463</v>
+      </c>
+      <c r="J122">
         <v>7.2</v>
       </c>
-    </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z122"/>
+      <c r="AA122"/>
+      <c r="AB122"/>
+      <c r="AC122"/>
+      <c r="AD122"/>
+      <c r="AE122"/>
+    </row>
+    <row r="123" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B123" t="s">
         <v>27</v>
       </c>
@@ -3478,11 +5255,20 @@
       <c r="H123" t="str">
         <v>9.0.13</v>
       </c>
-      <c r="I123">
+      <c r="I123" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="J123">
         <v>7.2</v>
       </c>
-    </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z123"/>
+      <c r="AA123"/>
+      <c r="AB123"/>
+      <c r="AC123"/>
+      <c r="AD123"/>
+      <c r="AE123"/>
+    </row>
+    <row r="124" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B124" t="s">
         <v>28</v>
       </c>
@@ -3492,11 +5278,20 @@
       <c r="H124" t="str">
         <v>9.0.12</v>
       </c>
-      <c r="I124">
+      <c r="I124" s="6" t="s">
+        <v>465</v>
+      </c>
+      <c r="J124">
         <v>7.2</v>
       </c>
-    </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z124"/>
+      <c r="AA124"/>
+      <c r="AB124"/>
+      <c r="AC124"/>
+      <c r="AD124"/>
+      <c r="AE124"/>
+    </row>
+    <row r="125" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B125" t="s">
         <v>30</v>
       </c>
@@ -3506,11 +5301,20 @@
       <c r="H125" t="str">
         <v>9.0.11</v>
       </c>
-      <c r="I125">
+      <c r="I125" s="6" t="s">
+        <v>466</v>
+      </c>
+      <c r="J125">
         <v>7</v>
       </c>
-    </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z125"/>
+      <c r="AA125"/>
+      <c r="AB125"/>
+      <c r="AC125"/>
+      <c r="AD125"/>
+      <c r="AE125"/>
+    </row>
+    <row r="126" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B126" t="s">
         <v>37</v>
       </c>
@@ -3520,11 +5324,20 @@
       <c r="H126" t="str">
         <v>9.0.10</v>
       </c>
-      <c r="I126">
+      <c r="I126" s="6" t="s">
+        <v>467</v>
+      </c>
+      <c r="J126">
         <v>7</v>
       </c>
-    </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z126"/>
+      <c r="AA126"/>
+      <c r="AB126"/>
+      <c r="AC126"/>
+      <c r="AD126"/>
+      <c r="AE126"/>
+    </row>
+    <row r="127" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>39</v>
       </c>
@@ -3541,11 +5354,20 @@
       <c r="H127" t="str">
         <v>9.0.8</v>
       </c>
-      <c r="I127">
+      <c r="I127" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="J127">
         <v>6.75</v>
       </c>
-    </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z127"/>
+      <c r="AA127"/>
+      <c r="AB127"/>
+      <c r="AC127"/>
+      <c r="AD127"/>
+      <c r="AE127"/>
+    </row>
+    <row r="128" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B128" t="s">
         <v>5</v>
       </c>
@@ -3555,11 +5377,20 @@
       <c r="H128" t="str">
         <v>9.0.7</v>
       </c>
-      <c r="I128">
+      <c r="I128" s="6" t="s">
+        <v>469</v>
+      </c>
+      <c r="J128">
         <v>7</v>
       </c>
-    </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z128"/>
+      <c r="AA128"/>
+      <c r="AB128"/>
+      <c r="AC128"/>
+      <c r="AD128"/>
+      <c r="AE128"/>
+    </row>
+    <row r="129" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B129" t="s">
         <v>14</v>
       </c>
@@ -3569,11 +5400,20 @@
       <c r="H129" t="str">
         <v>9.0.6</v>
       </c>
-      <c r="I129">
+      <c r="I129" s="6" t="s">
+        <v>470</v>
+      </c>
+      <c r="J129">
         <v>7</v>
       </c>
-    </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z129"/>
+      <c r="AA129"/>
+      <c r="AB129"/>
+      <c r="AC129"/>
+      <c r="AD129"/>
+      <c r="AE129"/>
+    </row>
+    <row r="130" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B130" t="s">
         <v>19</v>
       </c>
@@ -3583,11 +5423,20 @@
       <c r="H130" t="str">
         <v>9.0.5</v>
       </c>
-      <c r="I130">
+      <c r="I130" s="6" t="s">
+        <v>471</v>
+      </c>
+      <c r="J130">
         <v>7</v>
       </c>
-    </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z130"/>
+      <c r="AA130"/>
+      <c r="AB130"/>
+      <c r="AC130"/>
+      <c r="AD130"/>
+      <c r="AE130"/>
+    </row>
+    <row r="131" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B131" t="s">
         <v>23</v>
       </c>
@@ -3597,11 +5446,20 @@
       <c r="H131" t="str">
         <v>9.0.4</v>
       </c>
-      <c r="I131">
+      <c r="I131" s="6" t="s">
+        <v>472</v>
+      </c>
+      <c r="J131">
         <v>6.5</v>
       </c>
-    </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z131"/>
+      <c r="AA131"/>
+      <c r="AB131"/>
+      <c r="AC131"/>
+      <c r="AD131"/>
+      <c r="AE131"/>
+    </row>
+    <row r="132" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B132" t="s">
         <v>26</v>
       </c>
@@ -3611,11 +5469,20 @@
       <c r="H132" t="str">
         <v>9.0.2</v>
       </c>
-      <c r="I132">
+      <c r="I132" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="J132">
         <v>6.5</v>
       </c>
-    </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z132"/>
+      <c r="AA132"/>
+      <c r="AB132"/>
+      <c r="AC132"/>
+      <c r="AD132"/>
+      <c r="AE132"/>
+    </row>
+    <row r="133" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B133" t="s">
         <v>27</v>
       </c>
@@ -3625,11 +5492,20 @@
       <c r="H133" t="str">
         <v>9.0.1</v>
       </c>
-      <c r="I133">
+      <c r="I133" s="6" t="s">
+        <v>474</v>
+      </c>
+      <c r="J133">
         <v>6.5</v>
       </c>
-    </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z133"/>
+      <c r="AA133"/>
+      <c r="AB133"/>
+      <c r="AC133"/>
+      <c r="AD133"/>
+      <c r="AE133"/>
+    </row>
+    <row r="134" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B134" t="s">
         <v>28</v>
       </c>
@@ -3639,11 +5515,20 @@
       <c r="H134" t="str">
         <v>8.5.98</v>
       </c>
-      <c r="I134">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I134" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="J134">
+        <v>7.5</v>
+      </c>
+      <c r="Z134"/>
+      <c r="AA134"/>
+      <c r="AB134"/>
+      <c r="AC134"/>
+      <c r="AD134"/>
+      <c r="AE134"/>
+    </row>
+    <row r="135" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B135" t="s">
         <v>30</v>
       </c>
@@ -3653,11 +5538,20 @@
       <c r="H135" t="str">
         <v>8.5.97</v>
       </c>
-      <c r="I135">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I135" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="J135">
+        <v>7.5</v>
+      </c>
+      <c r="Z135"/>
+      <c r="AA135"/>
+      <c r="AB135"/>
+      <c r="AC135"/>
+      <c r="AD135"/>
+      <c r="AE135"/>
+    </row>
+    <row r="136" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B136" t="s">
         <v>37</v>
       </c>
@@ -3667,11 +5561,20 @@
       <c r="H136" t="str">
         <v>8.5.96</v>
       </c>
-      <c r="I136">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I136" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="J136">
+        <v>7.5</v>
+      </c>
+      <c r="Z136"/>
+      <c r="AA136"/>
+      <c r="AB136"/>
+      <c r="AC136"/>
+      <c r="AD136"/>
+      <c r="AE136"/>
+    </row>
+    <row r="137" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>40</v>
       </c>
@@ -3688,11 +5591,20 @@
       <c r="H137" t="str">
         <v>8.5.95</v>
       </c>
-      <c r="I137">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I137" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="J137">
+        <v>7.5</v>
+      </c>
+      <c r="Z137"/>
+      <c r="AA137"/>
+      <c r="AB137"/>
+      <c r="AC137"/>
+      <c r="AD137"/>
+      <c r="AE137"/>
+    </row>
+    <row r="138" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B138" t="s">
         <v>5</v>
       </c>
@@ -3702,11 +5614,20 @@
       <c r="H138" t="str">
         <v>8.5.94</v>
       </c>
-      <c r="I138">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I138" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="J138">
+        <v>7.5</v>
+      </c>
+      <c r="Z138"/>
+      <c r="AA138"/>
+      <c r="AB138"/>
+      <c r="AC138"/>
+      <c r="AD138"/>
+      <c r="AE138"/>
+    </row>
+    <row r="139" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B139" t="s">
         <v>14</v>
       </c>
@@ -3716,11 +5637,20 @@
       <c r="H139" t="str">
         <v>8.5.93</v>
       </c>
-      <c r="I139">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I139" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="J139">
+        <v>7.5</v>
+      </c>
+      <c r="Z139"/>
+      <c r="AA139"/>
+      <c r="AB139"/>
+      <c r="AC139"/>
+      <c r="AD139"/>
+      <c r="AE139"/>
+    </row>
+    <row r="140" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B140" t="s">
         <v>19</v>
       </c>
@@ -3730,11 +5660,20 @@
       <c r="H140" t="str">
         <v>8.5.92</v>
       </c>
-      <c r="I140">
+      <c r="I140" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="J140">
         <v>6.8</v>
       </c>
-    </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z140"/>
+      <c r="AA140"/>
+      <c r="AB140"/>
+      <c r="AC140"/>
+      <c r="AD140"/>
+      <c r="AE140"/>
+    </row>
+    <row r="141" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B141" t="s">
         <v>23</v>
       </c>
@@ -3744,11 +5683,20 @@
       <c r="H141" t="str">
         <v>8.5.91</v>
       </c>
-      <c r="I141">
+      <c r="I141" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="J141">
         <v>6.8</v>
       </c>
-    </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z141"/>
+      <c r="AA141"/>
+      <c r="AB141"/>
+      <c r="AC141"/>
+      <c r="AD141"/>
+      <c r="AE141"/>
+    </row>
+    <row r="142" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B142" t="s">
         <v>26</v>
       </c>
@@ -3758,11 +5706,20 @@
       <c r="H142" t="str">
         <v>8.5.90</v>
       </c>
-      <c r="I142">
+      <c r="I142" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="J142">
         <v>6.8</v>
       </c>
-    </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z142"/>
+      <c r="AA142"/>
+      <c r="AB142"/>
+      <c r="AC142"/>
+      <c r="AD142"/>
+      <c r="AE142"/>
+    </row>
+    <row r="143" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B143" t="s">
         <v>27</v>
       </c>
@@ -3772,11 +5729,20 @@
       <c r="H143" t="str">
         <v>8.5.89</v>
       </c>
-      <c r="I143">
+      <c r="I143" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="J143">
         <v>6.8</v>
       </c>
-    </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z143"/>
+      <c r="AA143"/>
+      <c r="AB143"/>
+      <c r="AC143"/>
+      <c r="AD143"/>
+      <c r="AE143"/>
+    </row>
+    <row r="144" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B144" t="s">
         <v>28</v>
       </c>
@@ -3786,11 +5752,20 @@
       <c r="H144" t="str">
         <v>8.5.88</v>
       </c>
-      <c r="I144">
+      <c r="I144" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="J144">
         <v>6.8</v>
       </c>
-    </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z144"/>
+      <c r="AA144"/>
+      <c r="AB144"/>
+      <c r="AC144"/>
+      <c r="AD144"/>
+      <c r="AE144"/>
+    </row>
+    <row r="145" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B145" t="s">
         <v>30</v>
       </c>
@@ -3800,11 +5775,20 @@
       <c r="H145" t="str">
         <v>8.5.87</v>
       </c>
-      <c r="I145">
+      <c r="I145" s="6" t="s">
+        <v>398</v>
+      </c>
+      <c r="J145">
         <v>6.5</v>
       </c>
-    </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z145"/>
+      <c r="AA145"/>
+      <c r="AB145"/>
+      <c r="AC145"/>
+      <c r="AD145"/>
+      <c r="AE145"/>
+    </row>
+    <row r="146" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B146" t="s">
         <v>41</v>
       </c>
@@ -3814,11 +5798,20 @@
       <c r="H146" t="str">
         <v>8.5.86</v>
       </c>
-      <c r="I146">
+      <c r="I146" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="J146">
         <v>6.5</v>
       </c>
-    </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z146"/>
+      <c r="AA146"/>
+      <c r="AB146"/>
+      <c r="AC146"/>
+      <c r="AD146"/>
+      <c r="AE146"/>
+    </row>
+    <row r="147" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>42</v>
       </c>
@@ -3835,11 +5828,20 @@
       <c r="H147" t="str">
         <v>8.5.85</v>
       </c>
-      <c r="I147">
+      <c r="I147" s="6" t="s">
+        <v>487</v>
+      </c>
+      <c r="J147">
         <v>6.5</v>
       </c>
-    </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z147"/>
+      <c r="AA147"/>
+      <c r="AB147"/>
+      <c r="AC147"/>
+      <c r="AD147"/>
+      <c r="AE147"/>
+    </row>
+    <row r="148" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B148" t="s">
         <v>5</v>
       </c>
@@ -3849,11 +5851,20 @@
       <c r="H148" t="str">
         <v>8.5.84</v>
       </c>
-      <c r="I148">
+      <c r="I148" s="6" t="s">
+        <v>488</v>
+      </c>
+      <c r="J148">
         <v>6.8</v>
       </c>
-    </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z148"/>
+      <c r="AA148"/>
+      <c r="AB148"/>
+      <c r="AC148"/>
+      <c r="AD148"/>
+      <c r="AE148"/>
+    </row>
+    <row r="149" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B149" t="s">
         <v>14</v>
       </c>
@@ -3863,11 +5874,20 @@
       <c r="H149" t="str">
         <v>8.5.83</v>
       </c>
-      <c r="I149">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I149" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="J149">
+        <v>7.5</v>
+      </c>
+      <c r="Z149"/>
+      <c r="AA149"/>
+      <c r="AB149"/>
+      <c r="AC149"/>
+      <c r="AD149"/>
+      <c r="AE149"/>
+    </row>
+    <row r="150" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B150" t="s">
         <v>19</v>
       </c>
@@ -3877,11 +5897,20 @@
       <c r="H150" t="str">
         <v>8.5.82</v>
       </c>
-      <c r="I150">
+      <c r="I150" s="6" t="s">
+        <v>489</v>
+      </c>
+      <c r="J150">
         <v>6.1</v>
       </c>
-    </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z150"/>
+      <c r="AA150"/>
+      <c r="AB150"/>
+      <c r="AC150"/>
+      <c r="AD150"/>
+      <c r="AE150"/>
+    </row>
+    <row r="151" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B151" t="s">
         <v>23</v>
       </c>
@@ -3891,11 +5920,20 @@
       <c r="H151" t="str">
         <v>8.5.81</v>
       </c>
-      <c r="I151">
+      <c r="I151" s="6" t="s">
+        <v>422</v>
+      </c>
+      <c r="J151">
         <v>6.1</v>
       </c>
-    </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z151"/>
+      <c r="AA151"/>
+      <c r="AB151"/>
+      <c r="AC151"/>
+      <c r="AD151"/>
+      <c r="AE151"/>
+    </row>
+    <row r="152" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B152" t="s">
         <v>26</v>
       </c>
@@ -3905,11 +5943,20 @@
       <c r="H152" t="str">
         <v>8.5.79</v>
       </c>
-      <c r="I152">
+      <c r="I152" s="6" t="s">
+        <v>490</v>
+      </c>
+      <c r="J152">
         <v>6.1</v>
       </c>
-    </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z152"/>
+      <c r="AA152"/>
+      <c r="AB152"/>
+      <c r="AC152"/>
+      <c r="AD152"/>
+      <c r="AE152"/>
+    </row>
+    <row r="153" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B153" t="s">
         <v>27</v>
       </c>
@@ -3919,11 +5966,20 @@
       <c r="H153" t="str">
         <v>8.5.78</v>
       </c>
-      <c r="I153">
+      <c r="I153" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="J153">
         <v>6.1</v>
       </c>
-    </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z153"/>
+      <c r="AA153"/>
+      <c r="AB153"/>
+      <c r="AC153"/>
+      <c r="AD153"/>
+      <c r="AE153"/>
+    </row>
+    <row r="154" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B154" t="s">
         <v>28</v>
       </c>
@@ -3933,11 +5989,20 @@
       <c r="H154" t="str">
         <v>8.5.77</v>
       </c>
-      <c r="I154">
+      <c r="I154" s="6" t="s">
+        <v>491</v>
+      </c>
+      <c r="J154">
         <v>6.1</v>
       </c>
-    </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z154"/>
+      <c r="AA154"/>
+      <c r="AB154"/>
+      <c r="AC154"/>
+      <c r="AD154"/>
+      <c r="AE154"/>
+    </row>
+    <row r="155" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B155" t="s">
         <v>30</v>
       </c>
@@ -3947,11 +6012,20 @@
       <c r="H155" t="str">
         <v>8.5.76</v>
       </c>
-      <c r="I155">
+      <c r="I155" s="6" t="s">
+        <v>492</v>
+      </c>
+      <c r="J155">
         <v>6.1</v>
       </c>
-    </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z155"/>
+      <c r="AA155"/>
+      <c r="AB155"/>
+      <c r="AC155"/>
+      <c r="AD155"/>
+      <c r="AE155"/>
+    </row>
+    <row r="156" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B156" t="s">
         <v>41</v>
       </c>
@@ -3961,11 +6035,20 @@
       <c r="H156" t="str">
         <v>8.5.75</v>
       </c>
-      <c r="I156">
+      <c r="I156" s="6" t="s">
+        <v>411</v>
+      </c>
+      <c r="J156">
         <v>6.1</v>
       </c>
-    </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z156"/>
+      <c r="AA156"/>
+      <c r="AB156"/>
+      <c r="AC156"/>
+      <c r="AD156"/>
+      <c r="AE156"/>
+    </row>
+    <row r="157" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>43</v>
       </c>
@@ -3982,11 +6065,20 @@
       <c r="H157" t="str">
         <v>8.5.73</v>
       </c>
-      <c r="I157">
+      <c r="I157" s="6" t="s">
+        <v>493</v>
+      </c>
+      <c r="J157">
         <v>6.1</v>
       </c>
-    </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z157"/>
+      <c r="AA157"/>
+      <c r="AB157"/>
+      <c r="AC157"/>
+      <c r="AD157"/>
+      <c r="AE157"/>
+    </row>
+    <row r="158" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B158" t="s">
         <v>5</v>
       </c>
@@ -3996,11 +6088,20 @@
       <c r="H158" t="str">
         <v>8.5.72</v>
       </c>
-      <c r="I158">
+      <c r="I158" s="6" t="s">
+        <v>494</v>
+      </c>
+      <c r="J158">
         <v>6.1</v>
       </c>
-    </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z158"/>
+      <c r="AA158"/>
+      <c r="AB158"/>
+      <c r="AC158"/>
+      <c r="AD158"/>
+      <c r="AE158"/>
+    </row>
+    <row r="159" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B159" t="s">
         <v>14</v>
       </c>
@@ -4010,11 +6111,20 @@
       <c r="H159" t="str">
         <v>8.5.71</v>
       </c>
-      <c r="I159">
+      <c r="I159" s="6" t="s">
+        <v>495</v>
+      </c>
+      <c r="J159">
         <v>6.1</v>
       </c>
-    </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z159"/>
+      <c r="AA159"/>
+      <c r="AB159"/>
+      <c r="AC159"/>
+      <c r="AD159"/>
+      <c r="AE159"/>
+    </row>
+    <row r="160" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B160" t="s">
         <v>19</v>
       </c>
@@ -4024,11 +6134,20 @@
       <c r="H160" t="str">
         <v>8.5.70</v>
       </c>
-      <c r="I160">
+      <c r="I160" s="6" t="s">
+        <v>496</v>
+      </c>
+      <c r="J160">
         <v>6.1</v>
       </c>
-    </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z160"/>
+      <c r="AA160"/>
+      <c r="AB160"/>
+      <c r="AC160"/>
+      <c r="AD160"/>
+      <c r="AE160"/>
+    </row>
+    <row r="161" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B161" t="s">
         <v>23</v>
       </c>
@@ -4038,11 +6157,20 @@
       <c r="H161" t="str">
         <v>8.5.69</v>
       </c>
-      <c r="I161">
+      <c r="I161" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="J161">
         <v>6.1</v>
       </c>
-    </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z161"/>
+      <c r="AA161"/>
+      <c r="AB161"/>
+      <c r="AC161"/>
+      <c r="AD161"/>
+      <c r="AE161"/>
+    </row>
+    <row r="162" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B162" t="s">
         <v>26</v>
       </c>
@@ -4052,11 +6180,20 @@
       <c r="H162" t="str">
         <v>8.5.68</v>
       </c>
-      <c r="I162">
+      <c r="I162" s="6" t="s">
+        <v>497</v>
+      </c>
+      <c r="J162">
         <v>6.1</v>
       </c>
-    </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z162"/>
+      <c r="AA162"/>
+      <c r="AB162"/>
+      <c r="AC162"/>
+      <c r="AD162"/>
+      <c r="AE162"/>
+    </row>
+    <row r="163" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B163" t="s">
         <v>27</v>
       </c>
@@ -4066,11 +6203,20 @@
       <c r="H163" t="str">
         <v>8.5.66</v>
       </c>
-      <c r="I163">
+      <c r="I163" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="J163">
         <v>6.1</v>
       </c>
-    </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z163"/>
+      <c r="AA163"/>
+      <c r="AB163"/>
+      <c r="AC163"/>
+      <c r="AD163"/>
+      <c r="AE163"/>
+    </row>
+    <row r="164" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B164" t="s">
         <v>28</v>
       </c>
@@ -4080,11 +6226,20 @@
       <c r="H164" t="str">
         <v>8.5.65</v>
       </c>
-      <c r="I164">
+      <c r="I164" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="J164">
         <v>6.1</v>
       </c>
-    </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z164"/>
+      <c r="AA164"/>
+      <c r="AB164"/>
+      <c r="AC164"/>
+      <c r="AD164"/>
+      <c r="AE164"/>
+    </row>
+    <row r="165" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B165" t="s">
         <v>30</v>
       </c>
@@ -4094,11 +6249,20 @@
       <c r="H165" t="str">
         <v>8.5.64</v>
       </c>
-      <c r="I165">
+      <c r="I165" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="J165">
         <v>6.1</v>
       </c>
-    </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z165"/>
+      <c r="AA165"/>
+      <c r="AB165"/>
+      <c r="AC165"/>
+      <c r="AD165"/>
+      <c r="AE165"/>
+    </row>
+    <row r="166" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B166" t="s">
         <v>41</v>
       </c>
@@ -4108,11 +6272,20 @@
       <c r="H166" t="str">
         <v>8.5.63</v>
       </c>
-      <c r="I166">
+      <c r="I166" s="6" t="s">
+        <v>498</v>
+      </c>
+      <c r="J166">
         <v>5.6999999999999993</v>
       </c>
-    </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z166"/>
+      <c r="AA166"/>
+      <c r="AB166"/>
+      <c r="AC166"/>
+      <c r="AD166"/>
+      <c r="AE166"/>
+    </row>
+    <row r="167" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B167" t="s">
         <v>44</v>
       </c>
@@ -4122,11 +6295,20 @@
       <c r="H167" t="str">
         <v>8.5.61</v>
       </c>
-      <c r="I167">
+      <c r="I167" s="6" t="s">
+        <v>429</v>
+      </c>
+      <c r="J167">
         <v>6.1</v>
       </c>
-    </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z167"/>
+      <c r="AA167"/>
+      <c r="AB167"/>
+      <c r="AC167"/>
+      <c r="AD167"/>
+      <c r="AE167"/>
+    </row>
+    <row r="168" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>45</v>
       </c>
@@ -4143,11 +6325,20 @@
       <c r="H168" t="str">
         <v>8.5.60</v>
       </c>
-      <c r="I168">
+      <c r="I168" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="J168">
         <v>6.55</v>
       </c>
-    </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z168"/>
+      <c r="AA168"/>
+      <c r="AB168"/>
+      <c r="AC168"/>
+      <c r="AD168"/>
+      <c r="AE168"/>
+    </row>
+    <row r="169" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B169" t="s">
         <v>5</v>
       </c>
@@ -4157,11 +6348,20 @@
       <c r="H169" t="str">
         <v>8.5.59</v>
       </c>
-      <c r="I169">
+      <c r="I169" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="J169">
         <v>6.1</v>
       </c>
-    </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z169"/>
+      <c r="AA169"/>
+      <c r="AB169"/>
+      <c r="AC169"/>
+      <c r="AD169"/>
+      <c r="AE169"/>
+    </row>
+    <row r="170" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B170" t="s">
         <v>14</v>
       </c>
@@ -4171,11 +6371,20 @@
       <c r="H170" t="str">
         <v>8.5.58</v>
       </c>
-      <c r="I170">
+      <c r="I170" s="6" t="s">
+        <v>450</v>
+      </c>
+      <c r="J170">
         <v>6.1</v>
       </c>
-    </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z170"/>
+      <c r="AA170"/>
+      <c r="AB170"/>
+      <c r="AC170"/>
+      <c r="AD170"/>
+      <c r="AE170"/>
+    </row>
+    <row r="171" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B171" t="s">
         <v>19</v>
       </c>
@@ -4185,11 +6394,20 @@
       <c r="H171" t="str">
         <v>8.5.57</v>
       </c>
-      <c r="I171">
+      <c r="I171" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="J171">
         <v>6.1</v>
       </c>
-    </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z171"/>
+      <c r="AA171"/>
+      <c r="AB171"/>
+      <c r="AC171"/>
+      <c r="AD171"/>
+      <c r="AE171"/>
+    </row>
+    <row r="172" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B172" t="s">
         <v>23</v>
       </c>
@@ -4199,11 +6417,20 @@
       <c r="H172" t="str">
         <v>8.5.56</v>
       </c>
-      <c r="I172">
+      <c r="I172" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="J172">
         <v>6.1</v>
       </c>
-    </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z172"/>
+      <c r="AA172"/>
+      <c r="AB172"/>
+      <c r="AC172"/>
+      <c r="AD172"/>
+      <c r="AE172"/>
+    </row>
+    <row r="173" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B173" t="s">
         <v>26</v>
       </c>
@@ -4213,11 +6440,20 @@
       <c r="H173" t="str">
         <v>8.5.55</v>
       </c>
-      <c r="I173">
+      <c r="I173" s="6" t="s">
+        <v>434</v>
+      </c>
+      <c r="J173">
         <v>6.1</v>
       </c>
-    </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z173"/>
+      <c r="AA173"/>
+      <c r="AB173"/>
+      <c r="AC173"/>
+      <c r="AD173"/>
+      <c r="AE173"/>
+    </row>
+    <row r="174" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B174" t="s">
         <v>27</v>
       </c>
@@ -4227,11 +6463,20 @@
       <c r="H174" t="str">
         <v>8.5.54</v>
       </c>
-      <c r="I174">
+      <c r="I174" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="J174">
         <v>6.1</v>
       </c>
-    </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z174"/>
+      <c r="AA174"/>
+      <c r="AB174"/>
+      <c r="AC174"/>
+      <c r="AD174"/>
+      <c r="AE174"/>
+    </row>
+    <row r="175" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B175" t="s">
         <v>28</v>
       </c>
@@ -4241,11 +6486,20 @@
       <c r="H175" t="str">
         <v>8.5.53</v>
       </c>
-      <c r="I175">
+      <c r="I175" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="J175">
         <v>6.1</v>
       </c>
-    </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z175"/>
+      <c r="AA175"/>
+      <c r="AB175"/>
+      <c r="AC175"/>
+      <c r="AD175"/>
+      <c r="AE175"/>
+    </row>
+    <row r="176" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B176" t="s">
         <v>30</v>
       </c>
@@ -4255,11 +6509,20 @@
       <c r="H176" t="str">
         <v>8.5.51</v>
       </c>
-      <c r="I176">
+      <c r="I176" s="6" t="s">
+        <v>451</v>
+      </c>
+      <c r="J176">
         <v>6.1</v>
       </c>
-    </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z176"/>
+      <c r="AA176"/>
+      <c r="AB176"/>
+      <c r="AC176"/>
+      <c r="AD176"/>
+      <c r="AE176"/>
+    </row>
+    <row r="177" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B177" t="s">
         <v>41</v>
       </c>
@@ -4269,11 +6532,20 @@
       <c r="H177" t="str">
         <v>8.5.50</v>
       </c>
-      <c r="I177">
+      <c r="I177" s="6" t="s">
+        <v>452</v>
+      </c>
+      <c r="J177">
         <v>6</v>
       </c>
-    </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z177"/>
+      <c r="AA177"/>
+      <c r="AB177"/>
+      <c r="AC177"/>
+      <c r="AD177"/>
+      <c r="AE177"/>
+    </row>
+    <row r="178" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B178" t="s">
         <v>44</v>
       </c>
@@ -4283,11 +6555,20 @@
       <c r="H178" t="str">
         <v>8.5.49</v>
       </c>
-      <c r="I178">
+      <c r="I178" s="6" t="s">
+        <v>499</v>
+      </c>
+      <c r="J178">
         <v>6.1</v>
       </c>
-    </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z178"/>
+      <c r="AA178"/>
+      <c r="AB178"/>
+      <c r="AC178"/>
+      <c r="AD178"/>
+      <c r="AE178"/>
+    </row>
+    <row r="179" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B179" t="s">
         <v>46</v>
       </c>
@@ -4297,11 +6578,20 @@
       <c r="H179" t="str">
         <v>8.5.47</v>
       </c>
-      <c r="I179">
+      <c r="I179" s="6" t="s">
+        <v>500</v>
+      </c>
+      <c r="J179">
         <v>7</v>
       </c>
-    </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z179"/>
+      <c r="AA179"/>
+      <c r="AB179"/>
+      <c r="AC179"/>
+      <c r="AD179"/>
+      <c r="AE179"/>
+    </row>
+    <row r="180" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>47</v>
       </c>
@@ -4318,11 +6608,20 @@
       <c r="H180" t="str">
         <v>8.5.46</v>
       </c>
-      <c r="I180">
+      <c r="I180" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="J180">
         <v>7</v>
       </c>
-    </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z180"/>
+      <c r="AA180"/>
+      <c r="AB180"/>
+      <c r="AC180"/>
+      <c r="AD180"/>
+      <c r="AE180"/>
+    </row>
+    <row r="181" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>48</v>
       </c>
@@ -4339,11 +6638,20 @@
       <c r="H181" t="str">
         <v>8.5.45</v>
       </c>
-      <c r="I181">
+      <c r="I181" s="6" t="s">
+        <v>501</v>
+      </c>
+      <c r="J181">
         <v>7</v>
       </c>
-    </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z181"/>
+      <c r="AA181"/>
+      <c r="AB181"/>
+      <c r="AC181"/>
+      <c r="AD181"/>
+      <c r="AE181"/>
+    </row>
+    <row r="182" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B182" t="s">
         <v>46</v>
       </c>
@@ -4353,11 +6661,20 @@
       <c r="H182" t="str">
         <v>8.5.43</v>
       </c>
-      <c r="I182">
+      <c r="I182" s="6" t="s">
+        <v>457</v>
+      </c>
+      <c r="J182">
         <v>7</v>
       </c>
-    </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z182"/>
+      <c r="AA182"/>
+      <c r="AB182"/>
+      <c r="AC182"/>
+      <c r="AD182"/>
+      <c r="AE182"/>
+    </row>
+    <row r="183" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>49</v>
       </c>
@@ -4374,11 +6691,20 @@
       <c r="H183" t="str">
         <v>8.5.42</v>
       </c>
-      <c r="I183">
+      <c r="I183" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="J183">
         <v>7</v>
       </c>
-    </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z183"/>
+      <c r="AA183"/>
+      <c r="AB183"/>
+      <c r="AC183"/>
+      <c r="AD183"/>
+      <c r="AE183"/>
+    </row>
+    <row r="184" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B184" t="s">
         <v>46</v>
       </c>
@@ -4388,11 +6714,20 @@
       <c r="H184" t="str">
         <v>8.5.41</v>
       </c>
-      <c r="I184">
+      <c r="I184" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="J184">
         <v>7</v>
       </c>
-    </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z184"/>
+      <c r="AA184"/>
+      <c r="AB184"/>
+      <c r="AC184"/>
+      <c r="AD184"/>
+      <c r="AE184"/>
+    </row>
+    <row r="185" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>50</v>
       </c>
@@ -4409,11 +6744,20 @@
       <c r="H185" t="str">
         <v>8.5.40</v>
       </c>
-      <c r="I185">
+      <c r="I185" s="6" t="s">
+        <v>502</v>
+      </c>
+      <c r="J185">
         <v>6.55</v>
       </c>
-    </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z185"/>
+      <c r="AA185"/>
+      <c r="AB185"/>
+      <c r="AC185"/>
+      <c r="AD185"/>
+      <c r="AE185"/>
+    </row>
+    <row r="186" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B186" t="s">
         <v>46</v>
       </c>
@@ -4423,11 +6767,20 @@
       <c r="H186" t="str">
         <v>8.5.39</v>
       </c>
-      <c r="I186">
+      <c r="I186" s="6" t="s">
+        <v>503</v>
+      </c>
+      <c r="J186">
         <v>6</v>
       </c>
-    </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z186"/>
+      <c r="AA186"/>
+      <c r="AB186"/>
+      <c r="AC186"/>
+      <c r="AD186"/>
+      <c r="AE186"/>
+    </row>
+    <row r="187" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>51</v>
       </c>
@@ -4444,11 +6797,20 @@
       <c r="H187" t="str">
         <v>8.5.38</v>
       </c>
-      <c r="I187">
+      <c r="I187" s="6" t="s">
+        <v>462</v>
+      </c>
+      <c r="J187">
         <v>6</v>
       </c>
-    </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z187"/>
+      <c r="AA187"/>
+      <c r="AB187"/>
+      <c r="AC187"/>
+      <c r="AD187"/>
+      <c r="AE187"/>
+    </row>
+    <row r="188" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B188" t="s">
         <v>46</v>
       </c>
@@ -4458,11 +6820,20 @@
       <c r="H188" t="str">
         <v>8.5.37</v>
       </c>
-      <c r="I188">
+      <c r="I188" s="6" t="s">
+        <v>504</v>
+      </c>
+      <c r="J188">
         <v>6.1</v>
       </c>
-    </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z188"/>
+      <c r="AA188"/>
+      <c r="AB188"/>
+      <c r="AC188"/>
+      <c r="AD188"/>
+      <c r="AE188"/>
+    </row>
+    <row r="189" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>52</v>
       </c>
@@ -4479,11 +6850,20 @@
       <c r="H189" t="str">
         <v>8.5.35</v>
       </c>
-      <c r="I189">
+      <c r="I189" s="6" t="s">
+        <v>505</v>
+      </c>
+      <c r="J189">
         <v>6.1</v>
       </c>
-    </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z189"/>
+      <c r="AA189"/>
+      <c r="AB189"/>
+      <c r="AC189"/>
+      <c r="AD189"/>
+      <c r="AE189"/>
+    </row>
+    <row r="190" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B190" t="s">
         <v>46</v>
       </c>
@@ -4493,11 +6873,20 @@
       <c r="H190" t="str">
         <v>8.5.34</v>
       </c>
-      <c r="I190">
+      <c r="I190" s="6" t="s">
+        <v>465</v>
+      </c>
+      <c r="J190">
         <v>6.1</v>
       </c>
-    </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z190"/>
+      <c r="AA190"/>
+      <c r="AB190"/>
+      <c r="AC190"/>
+      <c r="AD190"/>
+      <c r="AE190"/>
+    </row>
+    <row r="191" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>53</v>
       </c>
@@ -4514,11 +6903,20 @@
       <c r="H191" t="str">
         <v>8.5.33</v>
       </c>
-      <c r="I191">
+      <c r="I191" s="6" t="s">
+        <v>506</v>
+      </c>
+      <c r="J191">
         <v>6</v>
       </c>
-    </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z191"/>
+      <c r="AA191"/>
+      <c r="AB191"/>
+      <c r="AC191"/>
+      <c r="AD191"/>
+      <c r="AE191"/>
+    </row>
+    <row r="192" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B192" t="s">
         <v>46</v>
       </c>
@@ -4528,11 +6926,20 @@
       <c r="H192" t="str">
         <v>8.5.32</v>
       </c>
-      <c r="I192">
+      <c r="I192" s="6" t="s">
+        <v>467</v>
+      </c>
+      <c r="J192">
         <v>6</v>
       </c>
-    </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z192"/>
+      <c r="AA192"/>
+      <c r="AB192"/>
+      <c r="AC192"/>
+      <c r="AD192"/>
+      <c r="AE192"/>
+    </row>
+    <row r="193" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>54</v>
       </c>
@@ -4549,11 +6956,20 @@
       <c r="H193" t="str">
         <v>8.5.31</v>
       </c>
-      <c r="I193">
+      <c r="I193" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="J193">
         <v>5.9</v>
       </c>
-    </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z193"/>
+      <c r="AA193"/>
+      <c r="AB193"/>
+      <c r="AC193"/>
+      <c r="AD193"/>
+      <c r="AE193"/>
+    </row>
+    <row r="194" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B194" t="s">
         <v>46</v>
       </c>
@@ -4563,11 +6979,20 @@
       <c r="H194" t="str">
         <v>8.5.30</v>
       </c>
-      <c r="I194">
+      <c r="I194" s="6" t="s">
+        <v>469</v>
+      </c>
+      <c r="J194">
         <v>6</v>
       </c>
-    </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z194"/>
+      <c r="AA194"/>
+      <c r="AB194"/>
+      <c r="AC194"/>
+      <c r="AD194"/>
+      <c r="AE194"/>
+    </row>
+    <row r="195" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>55</v>
       </c>
@@ -4584,11 +7009,20 @@
       <c r="H195" t="str">
         <v>8.5.29</v>
       </c>
-      <c r="I195">
+      <c r="I195" s="6" t="s">
+        <v>470</v>
+      </c>
+      <c r="J195">
         <v>6</v>
       </c>
-    </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z195"/>
+      <c r="AA195"/>
+      <c r="AB195"/>
+      <c r="AC195"/>
+      <c r="AD195"/>
+      <c r="AE195"/>
+    </row>
+    <row r="196" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B196" t="s">
         <v>46</v>
       </c>
@@ -4598,11 +7032,20 @@
       <c r="H196" t="str">
         <v>8.5.28</v>
       </c>
-      <c r="I196">
+      <c r="I196" s="6" t="s">
+        <v>471</v>
+      </c>
+      <c r="J196">
         <v>6</v>
       </c>
-    </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z196"/>
+      <c r="AA196"/>
+      <c r="AB196"/>
+      <c r="AC196"/>
+      <c r="AD196"/>
+      <c r="AE196"/>
+    </row>
+    <row r="197" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>56</v>
       </c>
@@ -4619,11 +7062,20 @@
       <c r="H197" t="str">
         <v>8.5.27</v>
       </c>
-      <c r="I197">
+      <c r="I197" s="6" t="s">
+        <v>472</v>
+      </c>
+      <c r="J197">
         <v>6</v>
       </c>
-    </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z197"/>
+      <c r="AA197"/>
+      <c r="AB197"/>
+      <c r="AC197"/>
+      <c r="AD197"/>
+      <c r="AE197"/>
+    </row>
+    <row r="198" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B198" t="s">
         <v>46</v>
       </c>
@@ -4633,11 +7085,20 @@
       <c r="H198" t="str">
         <v>8.5.24</v>
       </c>
-      <c r="I198">
+      <c r="I198" s="6" t="s">
+        <v>507</v>
+      </c>
+      <c r="J198">
         <v>6</v>
       </c>
-    </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z198"/>
+      <c r="AA198"/>
+      <c r="AB198"/>
+      <c r="AC198"/>
+      <c r="AD198"/>
+      <c r="AE198"/>
+    </row>
+    <row r="199" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>57</v>
       </c>
@@ -4654,11 +7115,20 @@
       <c r="H199" t="str">
         <v>8.5.23</v>
       </c>
-      <c r="I199">
+      <c r="I199" s="6" t="s">
+        <v>508</v>
+      </c>
+      <c r="J199">
         <v>6</v>
       </c>
-    </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z199"/>
+      <c r="AA199"/>
+      <c r="AB199"/>
+      <c r="AC199"/>
+      <c r="AD199"/>
+      <c r="AE199"/>
+    </row>
+    <row r="200" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B200" t="s">
         <v>46</v>
       </c>
@@ -4668,11 +7138,20 @@
       <c r="H200" t="str">
         <v>8.5.21</v>
       </c>
-      <c r="I200">
+      <c r="I200" s="6" t="s">
+        <v>475</v>
+      </c>
+      <c r="J200">
         <v>6</v>
       </c>
-    </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z200"/>
+      <c r="AA200"/>
+      <c r="AB200"/>
+      <c r="AC200"/>
+      <c r="AD200"/>
+      <c r="AE200"/>
+    </row>
+    <row r="201" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>58</v>
       </c>
@@ -4689,11 +7168,20 @@
       <c r="H201" t="str">
         <v>8.5.20</v>
       </c>
-      <c r="I201">
+      <c r="I201" s="6" t="s">
+        <v>476</v>
+      </c>
+      <c r="J201">
         <v>6</v>
       </c>
-    </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z201"/>
+      <c r="AA201"/>
+      <c r="AB201"/>
+      <c r="AC201"/>
+      <c r="AD201"/>
+      <c r="AE201"/>
+    </row>
+    <row r="202" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B202" t="s">
         <v>46</v>
       </c>
@@ -4703,11 +7191,20 @@
       <c r="H202" t="str">
         <v>8.5.19</v>
       </c>
-      <c r="I202">
+      <c r="I202" s="6" t="s">
+        <v>477</v>
+      </c>
+      <c r="J202">
         <v>6</v>
       </c>
-    </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z202"/>
+      <c r="AA202"/>
+      <c r="AB202"/>
+      <c r="AC202"/>
+      <c r="AD202"/>
+      <c r="AE202"/>
+    </row>
+    <row r="203" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>59</v>
       </c>
@@ -4724,11 +7221,20 @@
       <c r="H203" t="str">
         <v>8.5.16</v>
       </c>
-      <c r="I203">
+      <c r="I203" s="6" t="s">
+        <v>478</v>
+      </c>
+      <c r="J203">
         <v>6</v>
       </c>
-    </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z203"/>
+      <c r="AA203"/>
+      <c r="AB203"/>
+      <c r="AC203"/>
+      <c r="AD203"/>
+      <c r="AE203"/>
+    </row>
+    <row r="204" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B204" t="s">
         <v>46</v>
       </c>
@@ -4738,11 +7244,20 @@
       <c r="H204" t="str">
         <v>8.5.15</v>
       </c>
-      <c r="I204">
+      <c r="I204" s="6" t="s">
+        <v>509</v>
+      </c>
+      <c r="J204">
         <v>6</v>
       </c>
-    </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z204"/>
+      <c r="AA204"/>
+      <c r="AB204"/>
+      <c r="AC204"/>
+      <c r="AD204"/>
+      <c r="AE204"/>
+    </row>
+    <row r="205" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>60</v>
       </c>
@@ -4759,11 +7274,20 @@
       <c r="H205" t="str">
         <v>8.5.14</v>
       </c>
-      <c r="I205">
+      <c r="I205" s="6" t="s">
+        <v>510</v>
+      </c>
+      <c r="J205">
         <v>6</v>
       </c>
-    </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z205"/>
+      <c r="AA205"/>
+      <c r="AB205"/>
+      <c r="AC205"/>
+      <c r="AD205"/>
+      <c r="AE205"/>
+    </row>
+    <row r="206" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B206" t="s">
         <v>46</v>
       </c>
@@ -4773,11 +7297,20 @@
       <c r="H206" t="str">
         <v>8.5.13</v>
       </c>
-      <c r="I206">
+      <c r="I206" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="J206">
         <v>6</v>
       </c>
-    </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z206"/>
+      <c r="AA206"/>
+      <c r="AB206"/>
+      <c r="AC206"/>
+      <c r="AD206"/>
+      <c r="AE206"/>
+    </row>
+    <row r="207" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>61</v>
       </c>
@@ -4794,11 +7327,20 @@
       <c r="H207" t="str">
         <v>8.5.12</v>
       </c>
-      <c r="I207">
+      <c r="I207" s="6" t="s">
+        <v>480</v>
+      </c>
+      <c r="J207">
         <v>6</v>
       </c>
-    </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z207"/>
+      <c r="AA207"/>
+      <c r="AB207"/>
+      <c r="AC207"/>
+      <c r="AD207"/>
+      <c r="AE207"/>
+    </row>
+    <row r="208" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B208" t="s">
         <v>46</v>
       </c>
@@ -4808,11 +7350,20 @@
       <c r="H208" t="str">
         <v>8.5.11</v>
       </c>
-      <c r="I208">
+      <c r="I208" s="6" t="s">
+        <v>481</v>
+      </c>
+      <c r="J208">
         <v>6</v>
       </c>
-    </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z208"/>
+      <c r="AA208"/>
+      <c r="AB208"/>
+      <c r="AC208"/>
+      <c r="AD208"/>
+      <c r="AE208"/>
+    </row>
+    <row r="209" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>62</v>
       </c>
@@ -4829,11 +7380,20 @@
       <c r="H209" t="str">
         <v>8.5.9</v>
       </c>
-      <c r="I209">
+      <c r="I209" s="6" t="s">
+        <v>482</v>
+      </c>
+      <c r="J209">
         <v>6</v>
       </c>
-    </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z209"/>
+      <c r="AA209"/>
+      <c r="AB209"/>
+      <c r="AC209"/>
+      <c r="AD209"/>
+      <c r="AE209"/>
+    </row>
+    <row r="210" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B210" t="s">
         <v>46</v>
       </c>
@@ -4843,11 +7403,20 @@
       <c r="H210" t="str">
         <v>8.5.8</v>
       </c>
-      <c r="I210">
+      <c r="I210" s="6" t="s">
+        <v>483</v>
+      </c>
+      <c r="J210">
         <v>6</v>
       </c>
-    </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="Z210"/>
+      <c r="AA210"/>
+      <c r="AB210"/>
+      <c r="AC210"/>
+      <c r="AD210"/>
+      <c r="AE210"/>
+    </row>
+    <row r="211" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>63</v>
       </c>
@@ -4864,11 +7433,14 @@
       <c r="H211" t="str">
         <v>8.5.6</v>
       </c>
-      <c r="I211">
+      <c r="I211" s="6" t="s">
+        <v>484</v>
+      </c>
+      <c r="J211">
         <v>6.1</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B212" t="s">
         <v>46</v>
       </c>
@@ -4878,11 +7450,14 @@
       <c r="H212" t="str">
         <v>8.5.5</v>
       </c>
-      <c r="I212">
+      <c r="I212" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="J212">
         <v>6.1</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>64</v>
       </c>
@@ -4899,11 +7474,14 @@
       <c r="H213" t="str">
         <v>8.5.4</v>
       </c>
-      <c r="I213">
+      <c r="I213" s="6" t="s">
+        <v>511</v>
+      </c>
+      <c r="J213">
         <v>6</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B214" t="s">
         <v>46</v>
       </c>
@@ -4913,11 +7491,14 @@
       <c r="H214" t="str">
         <v>8.5.3</v>
       </c>
-      <c r="I214">
+      <c r="I214" s="6" t="s">
+        <v>512</v>
+      </c>
+      <c r="J214">
         <v>6</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>65</v>
       </c>
@@ -4934,11 +7515,14 @@
       <c r="H215" t="str">
         <v>8.5.2</v>
       </c>
-      <c r="I215">
+      <c r="I215" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="J215">
         <v>6</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B216" t="s">
         <v>46</v>
       </c>
@@ -4948,11 +7532,14 @@
       <c r="H216" t="str">
         <v>8.5.0</v>
       </c>
-      <c r="I216">
+      <c r="I216" s="6" t="s">
+        <v>513</v>
+      </c>
+      <c r="J216">
         <v>6</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>66</v>
       </c>
@@ -4969,11 +7556,14 @@
       <c r="H217" t="str">
         <v>8.0.53</v>
       </c>
-      <c r="I217">
+      <c r="I217" s="6" t="s">
+        <v>514</v>
+      </c>
+      <c r="J217">
         <v>7.2</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B218" t="s">
         <v>46</v>
       </c>
@@ -4983,11 +7573,14 @@
       <c r="H218" t="str">
         <v>8.0.52</v>
       </c>
-      <c r="I218">
+      <c r="I218" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="J218">
         <v>6.45</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>67</v>
       </c>
@@ -5004,11 +7597,14 @@
       <c r="H219" t="str">
         <v>8.0.51</v>
       </c>
-      <c r="I219">
+      <c r="I219" s="6" t="s">
+        <v>516</v>
+      </c>
+      <c r="J219">
         <v>6.45</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B220" t="s">
         <v>46</v>
       </c>
@@ -5018,11 +7614,14 @@
       <c r="H220" t="str">
         <v>8.0.50</v>
       </c>
-      <c r="I220">
+      <c r="I220" s="6" t="s">
+        <v>517</v>
+      </c>
+      <c r="J220">
         <v>6.75</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B221" t="s">
         <v>68</v>
       </c>
@@ -5032,11 +7631,14 @@
       <c r="H221" t="str">
         <v>8.0.49</v>
       </c>
-      <c r="I221">
+      <c r="I221" s="6" t="s">
+        <v>518</v>
+      </c>
+      <c r="J221">
         <v>6.75</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B222" t="s">
         <v>69</v>
       </c>
@@ -5046,11 +7648,14 @@
       <c r="H222" t="str">
         <v>8.0.48</v>
       </c>
-      <c r="I222">
+      <c r="I222" s="6" t="s">
+        <v>519</v>
+      </c>
+      <c r="J222">
         <v>6.75</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>70</v>
       </c>
@@ -5067,11 +7672,14 @@
       <c r="H223" t="str">
         <v>8.0.47</v>
       </c>
-      <c r="I223">
+      <c r="I223" s="6" t="s">
+        <v>520</v>
+      </c>
+      <c r="J223">
         <v>6.75</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B224" t="s">
         <v>5</v>
       </c>
@@ -5081,11 +7689,14 @@
       <c r="H224" t="str">
         <v>8.0.46</v>
       </c>
-      <c r="I224">
+      <c r="I224" s="6" t="s">
+        <v>521</v>
+      </c>
+      <c r="J224">
         <v>6.75</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>71</v>
       </c>
@@ -5102,11 +7713,14 @@
       <c r="H225" t="str">
         <v>8.0.45</v>
       </c>
-      <c r="I225">
+      <c r="I225" s="6" t="s">
+        <v>522</v>
+      </c>
+      <c r="J225">
         <v>6.75</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B226" t="s">
         <v>5</v>
       </c>
@@ -5116,11 +7730,14 @@
       <c r="H226" t="str">
         <v>8.0.44</v>
       </c>
-      <c r="I226">
+      <c r="I226" s="6" t="s">
+        <v>523</v>
+      </c>
+      <c r="J226">
         <v>6.75</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>72</v>
       </c>
@@ -5137,11 +7754,14 @@
       <c r="H227" t="str">
         <v>8.0.43</v>
       </c>
-      <c r="I227">
+      <c r="I227" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="J227">
         <v>6.75</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B228" t="s">
         <v>8</v>
       </c>
@@ -5151,11 +7771,14 @@
       <c r="H228" t="str">
         <v>8.0.42</v>
       </c>
-      <c r="I228">
+      <c r="I228" s="6" t="s">
+        <v>480</v>
+      </c>
+      <c r="J228">
         <v>6.75</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B229" t="s">
         <v>5</v>
       </c>
@@ -5165,11 +7788,14 @@
       <c r="H229" t="str">
         <v>8.0.41</v>
       </c>
-      <c r="I229">
+      <c r="I229" s="6" t="s">
+        <v>525</v>
+      </c>
+      <c r="J229">
         <v>6.5</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>73</v>
       </c>
@@ -5186,11 +7812,14 @@
       <c r="H230" t="str">
         <v>8.0.39</v>
       </c>
-      <c r="I230">
+      <c r="I230" s="6" t="s">
+        <v>526</v>
+      </c>
+      <c r="J230">
         <v>6.5</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B231" t="s">
         <v>8</v>
       </c>
@@ -5200,11 +7829,14 @@
       <c r="H231" t="str">
         <v>8.0.38</v>
       </c>
-      <c r="I231">
+      <c r="I231" s="6" t="s">
+        <v>484</v>
+      </c>
+      <c r="J231">
         <v>6.5</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B232" t="s">
         <v>5</v>
       </c>
@@ -5214,11 +7846,14 @@
       <c r="H232" t="str">
         <v>8.0.37</v>
       </c>
-      <c r="I232">
+      <c r="I232" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="J232">
         <v>6.5</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>74</v>
       </c>
@@ -5235,11 +7870,14 @@
       <c r="H233" t="str">
         <v>8.0.36</v>
       </c>
-      <c r="I233">
+      <c r="I233" s="6" t="s">
+        <v>512</v>
+      </c>
+      <c r="J233">
         <v>6.5</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B234" t="s">
         <v>8</v>
       </c>
@@ -5249,11 +7887,14 @@
       <c r="H234" t="str">
         <v>8.0.35</v>
       </c>
-      <c r="I234">
+      <c r="I234" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="J234">
         <v>6.5</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B235" t="s">
         <v>5</v>
       </c>
@@ -5263,11 +7904,14 @@
       <c r="H235" t="str">
         <v>8.0.33</v>
       </c>
-      <c r="I235">
+      <c r="I235" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="J235">
         <v>6.5</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>75</v>
       </c>
@@ -5284,11 +7928,14 @@
       <c r="H236" t="str">
         <v>8.0.32</v>
       </c>
-      <c r="I236">
+      <c r="I236" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="J236">
         <v>6.5</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B237" t="s">
         <v>5</v>
       </c>
@@ -5298,11 +7945,14 @@
       <c r="H237" t="str">
         <v>8.0.30</v>
       </c>
-      <c r="I237">
+      <c r="I237" s="6" t="s">
+        <v>530</v>
+      </c>
+      <c r="J237">
         <v>6.5</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>76</v>
       </c>
@@ -5319,11 +7969,14 @@
       <c r="H238" t="str">
         <v>8.0.29</v>
       </c>
-      <c r="I238">
+      <c r="I238" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="J238">
         <v>6.5</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B239" t="s">
         <v>5</v>
       </c>
@@ -5333,11 +7986,14 @@
       <c r="H239" t="str">
         <v>8.0.28</v>
       </c>
-      <c r="I239">
+      <c r="I239" s="6" t="s">
+        <v>532</v>
+      </c>
+      <c r="J239">
         <v>6.5</v>
       </c>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>77</v>
       </c>
@@ -5354,11 +8010,14 @@
       <c r="H240" t="str">
         <v>8.0.27</v>
       </c>
-      <c r="I240">
+      <c r="I240" s="6" t="s">
+        <v>533</v>
+      </c>
+      <c r="J240">
         <v>6.5</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B241" t="s">
         <v>5</v>
       </c>
@@ -5368,11 +8027,14 @@
       <c r="H241" t="str">
         <v>8.0.26</v>
       </c>
-      <c r="I241">
+      <c r="I241" s="6" t="s">
+        <v>534</v>
+      </c>
+      <c r="J241">
         <v>6.5</v>
       </c>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B242" t="s">
         <v>14</v>
       </c>
@@ -5382,11 +8044,14 @@
       <c r="H242" t="str">
         <v>8.0.24</v>
       </c>
-      <c r="I242">
+      <c r="I242" s="6" t="s">
+        <v>535</v>
+      </c>
+      <c r="J242">
         <v>6.5</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>78</v>
       </c>
@@ -5403,11 +8068,14 @@
       <c r="H243" t="str">
         <v>8.0.24</v>
       </c>
-      <c r="I243">
+      <c r="I243" s="6" t="s">
+        <v>536</v>
+      </c>
+      <c r="J243">
         <v>6.5</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B244" t="s">
         <v>5</v>
       </c>
@@ -5417,11 +8085,14 @@
       <c r="H244" t="str">
         <v>8.0.22</v>
       </c>
-      <c r="I244">
+      <c r="I244" s="6" t="s">
+        <v>537</v>
+      </c>
+      <c r="J244">
         <v>6.5</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B245" t="s">
         <v>14</v>
       </c>
@@ -5431,11 +8102,14 @@
       <c r="H245" t="str">
         <v>8.0.21</v>
       </c>
-      <c r="I245">
+      <c r="I245" s="6" t="s">
+        <v>538</v>
+      </c>
+      <c r="J245">
         <v>6.5</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>79</v>
       </c>
@@ -5452,11 +8126,14 @@
       <c r="H246" t="str">
         <v>8.0.20</v>
       </c>
-      <c r="I246">
+      <c r="I246" s="6" t="s">
+        <v>539</v>
+      </c>
+      <c r="J246">
         <v>6.5</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B247" t="s">
         <v>5</v>
       </c>
@@ -5466,11 +8143,14 @@
       <c r="H247" t="str">
         <v>8.0.18</v>
       </c>
-      <c r="I247">
+      <c r="I247" s="6" t="s">
+        <v>540</v>
+      </c>
+      <c r="J247">
         <v>6.5</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B248" t="s">
         <v>14</v>
       </c>
@@ -5480,11 +8160,14 @@
       <c r="H248" t="str">
         <v>8.0.17</v>
       </c>
-      <c r="I248">
+      <c r="I248" s="6" t="s">
+        <v>541</v>
+      </c>
+      <c r="J248">
         <v>6.5</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>80</v>
       </c>
@@ -5501,11 +8184,14 @@
       <c r="H249" t="str">
         <v>8.0.15</v>
       </c>
-      <c r="I249">
+      <c r="I249" s="6" t="s">
+        <v>542</v>
+      </c>
+      <c r="J249">
         <v>6.5</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B250" t="s">
         <v>5</v>
       </c>
@@ -5515,11 +8201,14 @@
       <c r="H250" t="str">
         <v>8.0.14</v>
       </c>
-      <c r="I250">
+      <c r="I250" s="6" t="s">
+        <v>543</v>
+      </c>
+      <c r="J250">
         <v>6.5</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B251" t="s">
         <v>14</v>
       </c>
@@ -5529,11 +8218,14 @@
       <c r="H251" t="str">
         <v>8.0.12</v>
       </c>
-      <c r="I251">
+      <c r="I251" s="6" t="s">
+        <v>544</v>
+      </c>
+      <c r="J251">
         <v>6.5</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>81</v>
       </c>
@@ -5550,11 +8242,14 @@
       <c r="H252" t="str">
         <v>8.0.11</v>
       </c>
-      <c r="I252">
+      <c r="I252" s="6" t="s">
+        <v>545</v>
+      </c>
+      <c r="J252">
         <v>6.5</v>
       </c>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B253" t="s">
         <v>5</v>
       </c>
@@ -5564,11 +8259,14 @@
       <c r="H253" t="str">
         <v>8.0.9</v>
       </c>
-      <c r="I253">
+      <c r="I253" s="6" t="s">
+        <v>546</v>
+      </c>
+      <c r="J253">
         <v>6.5</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B254" t="s">
         <v>14</v>
       </c>
@@ -5578,11 +8276,14 @@
       <c r="H254" t="str">
         <v>8.0.8</v>
       </c>
-      <c r="I254">
+      <c r="I254" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="J254">
         <v>6.5</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B255" t="s">
         <v>19</v>
       </c>
@@ -5592,11 +8293,14 @@
       <c r="H255" t="str">
         <v>8.0.5</v>
       </c>
-      <c r="I255">
+      <c r="I255" s="6" t="s">
+        <v>548</v>
+      </c>
+      <c r="J255">
         <v>6.5</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>82</v>
       </c>
@@ -5613,11 +8317,14 @@
       <c r="H256" t="str">
         <v>8.0.3</v>
       </c>
-      <c r="I256">
+      <c r="I256" s="6" t="s">
+        <v>549</v>
+      </c>
+      <c r="J256">
         <v>6.2</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B257" t="s">
         <v>5</v>
       </c>
@@ -5627,11 +8334,14 @@
       <c r="H257" t="str">
         <v>8.0.1</v>
       </c>
-      <c r="I257">
+      <c r="I257" s="6" t="s">
+        <v>550</v>
+      </c>
+      <c r="J257">
         <v>6.2</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B258" t="s">
         <v>14</v>
       </c>
@@ -5641,11 +8351,14 @@
       <c r="H258" t="str">
         <v>7.0.106</v>
       </c>
-      <c r="I258">
+      <c r="I258" s="6" t="s">
+        <v>552</v>
+      </c>
+      <c r="J258">
         <v>6.45</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B259" t="s">
         <v>19</v>
       </c>
@@ -5655,11 +8368,14 @@
       <c r="H259" t="str">
         <v>7.0.105</v>
       </c>
-      <c r="I259">
+      <c r="I259" s="6" t="s">
+        <v>553</v>
+      </c>
+      <c r="J259">
         <v>6.45</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>83</v>
       </c>
@@ -5676,11 +8392,14 @@
       <c r="H260" t="str">
         <v>7.0.104</v>
       </c>
-      <c r="I260">
+      <c r="I260" s="6" t="s">
+        <v>554</v>
+      </c>
+      <c r="J260">
         <v>6.45</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B261" t="s">
         <v>5</v>
       </c>
@@ -5690,11 +8409,14 @@
       <c r="H261" t="str">
         <v>7.0.103</v>
       </c>
-      <c r="I261">
+      <c r="I261" s="6" t="s">
+        <v>555</v>
+      </c>
+      <c r="J261">
         <v>6.45</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B262" t="s">
         <v>14</v>
       </c>
@@ -5704,11 +8426,14 @@
       <c r="H262" t="str">
         <v>7.0.100</v>
       </c>
-      <c r="I262">
+      <c r="I262" s="6" t="s">
+        <v>556</v>
+      </c>
+      <c r="J262">
         <v>6.45</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B263" t="s">
         <v>19</v>
       </c>
@@ -5718,11 +8443,14 @@
       <c r="H263" t="str">
         <v>7.0.99</v>
       </c>
-      <c r="I263">
+      <c r="I263" s="6" t="s">
+        <v>557</v>
+      </c>
+      <c r="J263">
         <v>5.9</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>84</v>
       </c>
@@ -5739,11 +8467,14 @@
       <c r="H264" t="str">
         <v>7.0.96</v>
       </c>
-      <c r="I264">
+      <c r="I264" s="6" t="s">
+        <v>558</v>
+      </c>
+      <c r="J264">
         <v>7.2</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B265" t="s">
         <v>5</v>
       </c>
@@ -5753,11 +8484,14 @@
       <c r="H265" t="str">
         <v>7.0.94</v>
       </c>
-      <c r="I265">
+      <c r="I265" s="6" t="s">
+        <v>502</v>
+      </c>
+      <c r="J265">
         <v>7.2</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B266" t="s">
         <v>14</v>
       </c>
@@ -5767,11 +8501,14 @@
       <c r="H266" t="str">
         <v>7.0.93</v>
       </c>
-      <c r="I266">
+      <c r="I266" s="6" t="s">
+        <v>559</v>
+      </c>
+      <c r="J266">
         <v>6.45</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B267" t="s">
         <v>19</v>
       </c>
@@ -5781,11 +8518,14 @@
       <c r="H267" t="str">
         <v>7.0.92</v>
       </c>
-      <c r="I267">
+      <c r="I267" s="6" t="s">
+        <v>560</v>
+      </c>
+      <c r="J267">
         <v>6.45</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B268" t="s">
         <v>23</v>
       </c>
@@ -5795,11 +8535,14 @@
       <c r="H268" t="str">
         <v>7.0.91</v>
       </c>
-      <c r="I268">
+      <c r="I268" s="6" t="s">
+        <v>561</v>
+      </c>
+      <c r="J268">
         <v>6.45</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>85</v>
       </c>
@@ -5816,11 +8559,14 @@
       <c r="H269" t="str">
         <v>7.0.90</v>
       </c>
-      <c r="I269">
+      <c r="I269" s="6" t="s">
+        <v>562</v>
+      </c>
+      <c r="J269">
         <v>5.9</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B270" t="s">
         <v>5</v>
       </c>
@@ -5830,11 +8576,14 @@
       <c r="H270" t="str">
         <v>7.0.88</v>
       </c>
-      <c r="I270">
+      <c r="I270" s="6" t="s">
+        <v>563</v>
+      </c>
+      <c r="J270">
         <v>5.9</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B271" t="s">
         <v>14</v>
       </c>
@@ -5844,11 +8593,14 @@
       <c r="H271" t="str">
         <v>7.0.86</v>
       </c>
-      <c r="I271">
+      <c r="I271" s="6" t="s">
+        <v>516</v>
+      </c>
+      <c r="J271">
         <v>5.9</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B272" t="s">
         <v>19</v>
       </c>
@@ -5858,11 +8610,14 @@
       <c r="H272" t="str">
         <v>7.0.85</v>
       </c>
-      <c r="I272">
+      <c r="I272" s="6" t="s">
+        <v>517</v>
+      </c>
+      <c r="J272">
         <v>5.9</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B273" t="s">
         <v>23</v>
       </c>
@@ -5872,11 +8627,14 @@
       <c r="H273" t="str">
         <v>7.0.84</v>
       </c>
-      <c r="I273">
+      <c r="I273" s="6" t="s">
+        <v>518</v>
+      </c>
+      <c r="J273">
         <v>5.9</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>86</v>
       </c>
@@ -5893,11 +8651,14 @@
       <c r="H274" t="str">
         <v>7.0.82</v>
       </c>
-      <c r="I274">
+      <c r="I274" s="6" t="s">
+        <v>520</v>
+      </c>
+      <c r="J274">
         <v>5.9</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B275" t="s">
         <v>5</v>
       </c>
@@ -5907,11 +8668,14 @@
       <c r="H275" t="str">
         <v>7.0.81</v>
       </c>
-      <c r="I275">
+      <c r="I275" s="6" t="s">
+        <v>564</v>
+      </c>
+      <c r="J275">
         <v>5.9</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B276" t="s">
         <v>14</v>
       </c>
@@ -5921,11 +8685,14 @@
       <c r="H276" t="str">
         <v>7.0.79</v>
       </c>
-      <c r="I276">
+      <c r="I276" s="6" t="s">
+        <v>522</v>
+      </c>
+      <c r="J276">
         <v>5.9</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B277" t="s">
         <v>19</v>
       </c>
@@ -5935,11 +8702,14 @@
       <c r="H277" t="str">
         <v>7.0.78</v>
       </c>
-      <c r="I277">
+      <c r="I277" s="6" t="s">
+        <v>523</v>
+      </c>
+      <c r="J277">
         <v>5.9</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B278" t="s">
         <v>23</v>
       </c>
@@ -5949,11 +8719,14 @@
       <c r="H278" t="str">
         <v>7.0.77</v>
       </c>
-      <c r="I278">
+      <c r="I278" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="J278">
         <v>5.9</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B279" t="s">
         <v>26</v>
       </c>
@@ -5963,11 +8736,14 @@
       <c r="H279" t="str">
         <v>7.0.76</v>
       </c>
-      <c r="I279">
+      <c r="I279" s="6" t="s">
+        <v>565</v>
+      </c>
+      <c r="J279">
         <v>5.9</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B280" t="s">
         <v>27</v>
       </c>
@@ -5977,11 +8753,14 @@
       <c r="H280" t="str">
         <v>7.0.75</v>
       </c>
-      <c r="I280">
+      <c r="I280" s="6" t="s">
+        <v>525</v>
+      </c>
+      <c r="J280">
         <v>5.9</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B281" t="s">
         <v>28</v>
       </c>
@@ -5991,11 +8770,14 @@
       <c r="H281" t="str">
         <v>7.0.73</v>
       </c>
-      <c r="I281">
+      <c r="I281" s="6" t="s">
+        <v>566</v>
+      </c>
+      <c r="J281">
         <v>5.9</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>87</v>
       </c>
@@ -6012,11 +8794,14 @@
       <c r="H282" t="str">
         <v>7.0.72</v>
       </c>
-      <c r="I282">
+      <c r="I282" s="6" t="s">
+        <v>567</v>
+      </c>
+      <c r="J282">
         <v>5.9</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B283" t="s">
         <v>5</v>
       </c>
@@ -6026,11 +8811,14 @@
       <c r="H283" t="str">
         <v>7.0.70</v>
       </c>
-      <c r="I283">
+      <c r="I283" s="6" t="s">
+        <v>568</v>
+      </c>
+      <c r="J283">
         <v>5.9</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B284" t="s">
         <v>14</v>
       </c>
@@ -6040,11 +8828,14 @@
       <c r="H284" t="str">
         <v>7.0.69</v>
       </c>
-      <c r="I284">
+      <c r="I284" s="6" t="s">
+        <v>569</v>
+      </c>
+      <c r="J284">
         <v>5.9</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B285" t="s">
         <v>19</v>
       </c>
@@ -6054,11 +8845,14 @@
       <c r="H285" t="str">
         <v>7.0.68</v>
       </c>
-      <c r="I285">
+      <c r="I285" s="6" t="s">
+        <v>570</v>
+      </c>
+      <c r="J285">
         <v>5.9</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B286" t="s">
         <v>23</v>
       </c>
@@ -6068,11 +8862,14 @@
       <c r="H286" t="str">
         <v>7.0.67</v>
       </c>
-      <c r="I286">
+      <c r="I286" s="6" t="s">
+        <v>571</v>
+      </c>
+      <c r="J286">
         <v>5.9</v>
       </c>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B287" t="s">
         <v>26</v>
       </c>
@@ -6082,11 +8879,14 @@
       <c r="H287" t="str">
         <v>7.0.65</v>
       </c>
-      <c r="I287">
+      <c r="I287" s="6" t="s">
+        <v>572</v>
+      </c>
+      <c r="J287">
         <v>5.9</v>
       </c>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B288" t="s">
         <v>27</v>
       </c>
@@ -6096,11 +8896,14 @@
       <c r="H288" t="str">
         <v>7.0.64</v>
       </c>
-      <c r="I288">
+      <c r="I288" s="6" t="s">
+        <v>573</v>
+      </c>
+      <c r="J288">
         <v>5.9</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B289" t="s">
         <v>28</v>
       </c>
@@ -6110,11 +8913,14 @@
       <c r="H289" t="str">
         <v>7.0.63</v>
       </c>
-      <c r="I289">
+      <c r="I289" s="6" t="s">
+        <v>574</v>
+      </c>
+      <c r="J289">
         <v>5.9</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B290" t="s">
         <v>30</v>
       </c>
@@ -6124,11 +8930,14 @@
       <c r="H290" t="str">
         <v>7.0.62</v>
       </c>
-      <c r="I290">
+      <c r="I290" s="6" t="s">
+        <v>575</v>
+      </c>
+      <c r="J290">
         <v>5.9</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>88</v>
       </c>
@@ -6145,11 +8954,14 @@
       <c r="H291" t="str">
         <v>7.0.61</v>
       </c>
-      <c r="I291">
+      <c r="I291" s="6" t="s">
+        <v>576</v>
+      </c>
+      <c r="J291">
         <v>5.9</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B292" t="s">
         <v>5</v>
       </c>
@@ -6159,11 +8971,14 @@
       <c r="H292" t="str">
         <v>7.0.59</v>
       </c>
-      <c r="I292">
+      <c r="I292" s="6" t="s">
+        <v>577</v>
+      </c>
+      <c r="J292">
         <v>5.9</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B293" t="s">
         <v>14</v>
       </c>
@@ -6173,11 +8988,14 @@
       <c r="H293" t="str">
         <v>7.0.57</v>
       </c>
-      <c r="I293">
+      <c r="I293" s="6" t="s">
+        <v>578</v>
+      </c>
+      <c r="J293">
         <v>5.9</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B294" t="s">
         <v>19</v>
       </c>
@@ -6187,11 +9005,14 @@
       <c r="H294" t="str">
         <v>7.0.56</v>
       </c>
-      <c r="I294">
+      <c r="I294" s="6" t="s">
+        <v>579</v>
+      </c>
+      <c r="J294">
         <v>5.9</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B295" t="s">
         <v>23</v>
       </c>
@@ -6201,11 +9022,14 @@
       <c r="H295" t="str">
         <v>7.0.55</v>
       </c>
-      <c r="I295">
+      <c r="I295" s="6" t="s">
+        <v>580</v>
+      </c>
+      <c r="J295">
         <v>5.9</v>
       </c>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B296" t="s">
         <v>26</v>
       </c>
@@ -6215,11 +9039,14 @@
       <c r="H296" t="str">
         <v>7.0.54</v>
       </c>
-      <c r="I296">
+      <c r="I296" s="6" t="s">
+        <v>581</v>
+      </c>
+      <c r="J296">
         <v>5.9</v>
       </c>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B297" t="s">
         <v>27</v>
       </c>
@@ -6229,11 +9056,14 @@
       <c r="H297" t="str">
         <v>7.0.53</v>
       </c>
-      <c r="I297">
+      <c r="I297" s="6" t="s">
+        <v>582</v>
+      </c>
+      <c r="J297">
         <v>5.9</v>
       </c>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B298" t="s">
         <v>28</v>
       </c>
@@ -6243,11 +9073,14 @@
       <c r="H298" t="str">
         <v>7.0.52</v>
       </c>
-      <c r="I298">
+      <c r="I298" s="6" t="s">
+        <v>583</v>
+      </c>
+      <c r="J298">
         <v>5.9</v>
       </c>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B299" t="s">
         <v>30</v>
       </c>
@@ -6257,11 +9090,14 @@
       <c r="H299" t="str">
         <v>7.0.50</v>
       </c>
-      <c r="I299">
+      <c r="I299" s="6" t="s">
+        <v>551</v>
+      </c>
+      <c r="J299">
         <v>5.9</v>
       </c>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
         <v>89</v>
       </c>
@@ -6278,11 +9114,14 @@
       <c r="H300" t="str">
         <v>7.0.47</v>
       </c>
-      <c r="I300">
+      <c r="I300" s="6" t="s">
+        <v>584</v>
+      </c>
+      <c r="J300">
         <v>5.9</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B301" t="s">
         <v>5</v>
       </c>
@@ -6292,11 +9131,14 @@
       <c r="H301" t="str">
         <v>7.0.42</v>
       </c>
-      <c r="I301">
+      <c r="I301" s="6" t="s">
+        <v>585</v>
+      </c>
+      <c r="J301">
         <v>5.9</v>
       </c>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B302" t="s">
         <v>14</v>
       </c>
@@ -6306,11 +9148,14 @@
       <c r="H302" t="str">
         <v>7.0.41</v>
       </c>
-      <c r="I302">
+      <c r="I302" s="6" t="s">
+        <v>586</v>
+      </c>
+      <c r="J302">
         <v>5.9</v>
       </c>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B303" t="s">
         <v>19</v>
       </c>
@@ -6320,11 +9165,14 @@
       <c r="H303" t="str">
         <v>7.0.40</v>
       </c>
-      <c r="I303">
+      <c r="I303" s="6" t="s">
+        <v>587</v>
+      </c>
+      <c r="J303">
         <v>5.9</v>
       </c>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B304" t="s">
         <v>23</v>
       </c>
@@ -6334,11 +9182,14 @@
       <c r="H304" t="str">
         <v>7.0.39</v>
       </c>
-      <c r="I304">
+      <c r="I304" s="6" t="s">
+        <v>588</v>
+      </c>
+      <c r="J304">
         <v>5.9</v>
       </c>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B305" t="s">
         <v>26</v>
       </c>
@@ -6348,11 +9199,14 @@
       <c r="H305" t="str">
         <v>7.0.37</v>
       </c>
-      <c r="I305">
+      <c r="I305" s="6" t="s">
+        <v>589</v>
+      </c>
+      <c r="J305">
         <v>5.9</v>
       </c>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B306" t="s">
         <v>27</v>
       </c>
@@ -6362,11 +9216,14 @@
       <c r="H306" t="str">
         <v>7.0.35</v>
       </c>
-      <c r="I306">
+      <c r="I306" s="6" t="s">
+        <v>590</v>
+      </c>
+      <c r="J306">
         <v>5.9</v>
       </c>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B307" t="s">
         <v>28</v>
       </c>
@@ -6376,11 +9233,14 @@
       <c r="H307" t="str">
         <v>7.0.34</v>
       </c>
-      <c r="I307">
+      <c r="I307" s="6" t="s">
+        <v>591</v>
+      </c>
+      <c r="J307">
         <v>6.2</v>
       </c>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B308" t="s">
         <v>30</v>
       </c>
@@ -6390,11 +9250,14 @@
       <c r="H308" t="str">
         <v>7.0.33</v>
       </c>
-      <c r="I308">
+      <c r="I308" s="6" t="s">
+        <v>592</v>
+      </c>
+      <c r="J308">
         <v>6.2</v>
       </c>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
         <v>90</v>
       </c>
@@ -6411,11 +9274,14 @@
       <c r="H309" t="str">
         <v>7.0.32</v>
       </c>
-      <c r="I309">
+      <c r="I309" s="6" t="s">
+        <v>593</v>
+      </c>
+      <c r="J309">
         <v>6.2</v>
       </c>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B310" t="s">
         <v>5</v>
       </c>
@@ -6425,11 +9291,14 @@
       <c r="H310" t="str">
         <v>7.0.30</v>
       </c>
-      <c r="I310">
+      <c r="I310" s="6" t="s">
+        <v>594</v>
+      </c>
+      <c r="J310">
         <v>6.2</v>
       </c>
     </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B311" t="s">
         <v>14</v>
       </c>
@@ -6439,11 +9308,14 @@
       <c r="H311" t="str">
         <v>7.0.29</v>
       </c>
-      <c r="I311">
+      <c r="I311" s="6" t="s">
+        <v>595</v>
+      </c>
+      <c r="J311">
         <v>6.2</v>
       </c>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B312" t="s">
         <v>19</v>
       </c>
@@ -6453,11 +9325,14 @@
       <c r="H312" t="str">
         <v>7.0.28</v>
       </c>
-      <c r="I312">
+      <c r="I312" s="6" t="s">
+        <v>596</v>
+      </c>
+      <c r="J312">
         <v>6.2</v>
       </c>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B313" t="s">
         <v>23</v>
       </c>
@@ -6467,11 +9342,14 @@
       <c r="H313" t="str">
         <v>7.0.27</v>
       </c>
-      <c r="I313">
+      <c r="I313" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="J313">
         <v>5.9</v>
       </c>
     </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B314" t="s">
         <v>26</v>
       </c>
@@ -6481,11 +9359,14 @@
       <c r="H314" t="str">
         <v>7.0.26</v>
       </c>
-      <c r="I314">
+      <c r="I314" s="6" t="s">
+        <v>598</v>
+      </c>
+      <c r="J314">
         <v>5.9</v>
       </c>
     </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B315" t="s">
         <v>27</v>
       </c>
@@ -6495,11 +9376,14 @@
       <c r="H315" t="str">
         <v>7.0.25</v>
       </c>
-      <c r="I315">
+      <c r="I315" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="J315">
         <v>5.9</v>
       </c>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B316" t="s">
         <v>28</v>
       </c>
@@ -6509,11 +9393,14 @@
       <c r="H316" t="str">
         <v>7.0.23</v>
       </c>
-      <c r="I316">
+      <c r="I316" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="J316">
         <v>5.9</v>
       </c>
     </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B317" t="s">
         <v>30</v>
       </c>
@@ -6523,11 +9410,14 @@
       <c r="H317" t="str">
         <v>7.0.22</v>
       </c>
-      <c r="I317">
+      <c r="I317" s="6" t="s">
+        <v>601</v>
+      </c>
+      <c r="J317">
         <v>6.2</v>
       </c>
     </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
         <v>91</v>
       </c>
@@ -6544,11 +9434,14 @@
       <c r="H318" t="str">
         <v>7.0.21</v>
       </c>
-      <c r="I318">
+      <c r="I318" s="6" t="s">
+        <v>602</v>
+      </c>
+      <c r="J318">
         <v>6.2</v>
       </c>
     </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B319" t="s">
         <v>5</v>
       </c>
@@ -6558,11 +9451,14 @@
       <c r="H319" t="str">
         <v>7.0.20</v>
       </c>
-      <c r="I319">
+      <c r="I319" s="6" t="s">
+        <v>603</v>
+      </c>
+      <c r="J319">
         <v>6.2</v>
       </c>
     </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B320" t="s">
         <v>14</v>
       </c>
@@ -6572,11 +9468,14 @@
       <c r="H320" t="str">
         <v>7.0.19</v>
       </c>
-      <c r="I320">
+      <c r="I320" s="6" t="s">
+        <v>604</v>
+      </c>
+      <c r="J320">
         <v>6.2</v>
       </c>
     </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B321" t="s">
         <v>19</v>
       </c>
@@ -6586,11 +9485,14 @@
       <c r="H321" t="str">
         <v>7.0.16</v>
       </c>
-      <c r="I321">
+      <c r="I321" s="6" t="s">
+        <v>605</v>
+      </c>
+      <c r="J321">
         <v>6.2</v>
       </c>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B322" t="s">
         <v>23</v>
       </c>
@@ -6600,11 +9502,14 @@
       <c r="H322" t="str">
         <v>7.0.14</v>
       </c>
-      <c r="I322">
+      <c r="I322" s="6" t="s">
+        <v>606</v>
+      </c>
+      <c r="J322">
         <v>6.2</v>
       </c>
     </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B323" t="s">
         <v>26</v>
       </c>
@@ -6614,11 +9519,14 @@
       <c r="H323" t="str">
         <v>7.0.12</v>
       </c>
-      <c r="I323">
+      <c r="I323" s="6" t="s">
+        <v>607</v>
+      </c>
+      <c r="J323">
         <v>6.2</v>
       </c>
     </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B324" t="s">
         <v>27</v>
       </c>
@@ -6628,11 +9536,14 @@
       <c r="H324" t="str">
         <v>7.0.11</v>
       </c>
-      <c r="I324">
+      <c r="I324" s="6" t="s">
+        <v>608</v>
+      </c>
+      <c r="J324">
         <v>6.2</v>
       </c>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B325" t="s">
         <v>28</v>
       </c>
@@ -6642,11 +9553,14 @@
       <c r="H325" t="str">
         <v>7.0.8</v>
       </c>
-      <c r="I325">
+      <c r="I325" s="6" t="s">
+        <v>609</v>
+      </c>
+      <c r="J325">
         <v>6.2</v>
       </c>
     </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B326" t="s">
         <v>30</v>
       </c>
@@ -6656,11 +9570,14 @@
       <c r="H326" t="str">
         <v>7.0.6</v>
       </c>
-      <c r="I326">
+      <c r="I326" s="6" t="s">
+        <v>610</v>
+      </c>
+      <c r="J326">
         <v>6.2</v>
       </c>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
         <v>92</v>
       </c>
@@ -6677,11 +9594,14 @@
       <c r="H327" t="str">
         <v>7.0.5</v>
       </c>
-      <c r="I327">
+      <c r="I327" s="6" t="s">
+        <v>611</v>
+      </c>
+      <c r="J327">
         <v>6.2</v>
       </c>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B328" t="s">
         <v>5</v>
       </c>
@@ -6691,11 +9611,14 @@
       <c r="H328" t="str">
         <v>7.0.4</v>
       </c>
-      <c r="I328">
+      <c r="I328" s="6" t="s">
+        <v>612</v>
+      </c>
+      <c r="J328">
         <v>6.2</v>
       </c>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B329" t="s">
         <v>14</v>
       </c>
@@ -6705,11 +9628,14 @@
       <c r="H329" t="str">
         <v>7.0.2</v>
       </c>
-      <c r="I329">
+      <c r="I329" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="J329">
         <v>6.2</v>
       </c>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B330" t="s">
         <v>19</v>
       </c>
@@ -6719,11 +9645,14 @@
       <c r="H330" t="str">
         <v>7.0.0</v>
       </c>
-      <c r="I330">
+      <c r="I330" s="6" t="s">
+        <v>614</v>
+      </c>
+      <c r="J330">
         <v>6.2</v>
       </c>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B331" t="s">
         <v>23</v>
       </c>
@@ -6731,7 +9660,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B332" t="s">
         <v>26</v>
       </c>
@@ -6739,7 +9668,7 @@
         <v>5.3</v>
       </c>
     </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B333" t="s">
         <v>27</v>
       </c>
@@ -6747,7 +9676,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B334" t="s">
         <v>28</v>
       </c>
@@ -6755,7 +9684,7 @@
         <v>5.3</v>
       </c>
     </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B335" t="s">
         <v>30</v>
       </c>
@@ -6763,7 +9692,7 @@
         <v>6.1</v>
       </c>
     </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B336" t="s">
         <v>35</v>
       </c>
@@ -10877,7 +13806,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="817" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="817" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B817" t="s">
         <v>136</v>
       </c>
@@ -10885,7 +13814,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="818" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="818" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A818" t="s">
         <v>137</v>
       </c>
@@ -10900,7 +13829,7 @@
         <v>7.45</v>
       </c>
     </row>
-    <row r="819" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="819" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B819" t="s">
         <v>5</v>
       </c>
@@ -10916,18 +13845,21 @@
       <c r="Q819" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="R819" s="4" t="s">
+      <c r="R819" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="S819" s="4" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="820" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="820" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B820" t="s">
         <v>14</v>
       </c>
       <c r="C820">
         <v>7.5</v>
       </c>
-      <c r="O820" s="5" t="s">
+      <c r="O820" s="7" t="s">
         <v>137</v>
       </c>
       <c r="P820" s="2" t="s">
@@ -10936,252 +13868,270 @@
       <c r="Q820" s="2">
         <v>8.1</v>
       </c>
-      <c r="R820" s="8">
+      <c r="R820" s="13" t="s">
+        <v>455</v>
+      </c>
+      <c r="S820" s="10">
         <f>MEDIAN(Q820:Q837)</f>
         <v>7.45</v>
       </c>
     </row>
-    <row r="821" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="821" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B821" t="s">
         <v>19</v>
       </c>
       <c r="C821">
         <v>7.5</v>
       </c>
-      <c r="O821" s="6"/>
+      <c r="O821" s="8"/>
       <c r="P821" s="2" t="s">
         <v>5</v>
       </c>
       <c r="Q821" s="2">
         <v>8.1</v>
       </c>
-      <c r="R821" s="9"/>
-    </row>
-    <row r="822" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="R821" s="13"/>
+      <c r="S821" s="11"/>
+    </row>
+    <row r="822" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B822" t="s">
         <v>23</v>
       </c>
       <c r="C822">
         <v>7.5</v>
       </c>
-      <c r="O822" s="6"/>
+      <c r="O822" s="8"/>
       <c r="P822" s="2" t="s">
         <v>14</v>
       </c>
       <c r="Q822" s="2">
         <v>7.5</v>
       </c>
-      <c r="R822" s="9"/>
-    </row>
-    <row r="823" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="R822" s="13"/>
+      <c r="S822" s="11"/>
+    </row>
+    <row r="823" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B823" t="s">
         <v>26</v>
       </c>
       <c r="C823">
         <v>5.3</v>
       </c>
-      <c r="O823" s="6"/>
+      <c r="O823" s="8"/>
       <c r="P823" s="2" t="s">
         <v>19</v>
       </c>
       <c r="Q823" s="2">
         <v>7.5</v>
       </c>
-      <c r="R823" s="9"/>
-    </row>
-    <row r="824" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="R823" s="13"/>
+      <c r="S823" s="11"/>
+    </row>
+    <row r="824" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B824" t="s">
         <v>27</v>
       </c>
       <c r="C824">
         <v>7.5</v>
       </c>
-      <c r="O824" s="6"/>
+      <c r="O824" s="8"/>
       <c r="P824" s="2" t="s">
         <v>23</v>
       </c>
       <c r="Q824" s="2">
         <v>7.5</v>
       </c>
-      <c r="R824" s="9"/>
-    </row>
-    <row r="825" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="R824" s="13"/>
+      <c r="S824" s="11"/>
+    </row>
+    <row r="825" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B825" t="s">
         <v>28</v>
       </c>
       <c r="C825">
         <v>5.3</v>
       </c>
-      <c r="O825" s="6"/>
+      <c r="O825" s="8"/>
       <c r="P825" s="2" t="s">
         <v>26</v>
       </c>
       <c r="Q825" s="2">
         <v>5.3</v>
       </c>
-      <c r="R825" s="9"/>
-    </row>
-    <row r="826" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="R825" s="13"/>
+      <c r="S825" s="11"/>
+    </row>
+    <row r="826" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B826" t="s">
         <v>30</v>
       </c>
       <c r="C826">
         <v>6.1</v>
       </c>
-      <c r="O826" s="6"/>
+      <c r="O826" s="8"/>
       <c r="P826" s="2" t="s">
         <v>27</v>
       </c>
       <c r="Q826" s="2">
         <v>7.5</v>
       </c>
-      <c r="R826" s="9"/>
-    </row>
-    <row r="827" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="R826" s="13"/>
+      <c r="S826" s="11"/>
+    </row>
+    <row r="827" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B827" t="s">
         <v>41</v>
       </c>
       <c r="C827">
         <v>6.5</v>
       </c>
-      <c r="O827" s="6"/>
+      <c r="O827" s="8"/>
       <c r="P827" s="2" t="s">
         <v>28</v>
       </c>
       <c r="Q827" s="2">
         <v>5.3</v>
       </c>
-      <c r="R827" s="9"/>
-    </row>
-    <row r="828" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="R827" s="13"/>
+      <c r="S827" s="11"/>
+    </row>
+    <row r="828" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B828" t="s">
         <v>46</v>
       </c>
       <c r="C828">
         <v>4.8</v>
       </c>
-      <c r="O828" s="6"/>
+      <c r="O828" s="8"/>
       <c r="P828" s="2" t="s">
         <v>30</v>
       </c>
       <c r="Q828" s="2">
         <v>6.1</v>
       </c>
-      <c r="R828" s="9"/>
-    </row>
-    <row r="829" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="R828" s="13"/>
+      <c r="S828" s="11"/>
+    </row>
+    <row r="829" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B829" t="s">
         <v>68</v>
       </c>
       <c r="C829">
         <v>7</v>
       </c>
-      <c r="O829" s="6"/>
+      <c r="O829" s="8"/>
       <c r="P829" s="2" t="s">
         <v>41</v>
       </c>
       <c r="Q829" s="2">
         <v>6.5</v>
       </c>
-      <c r="R829" s="9"/>
-    </row>
-    <row r="830" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="R829" s="13"/>
+      <c r="S829" s="11"/>
+    </row>
+    <row r="830" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B830" t="s">
         <v>69</v>
       </c>
       <c r="C830">
         <v>7.5</v>
       </c>
-      <c r="O830" s="6"/>
+      <c r="O830" s="8"/>
       <c r="P830" s="2" t="s">
         <v>46</v>
       </c>
       <c r="Q830" s="2">
         <v>4.8</v>
       </c>
-      <c r="R830" s="9"/>
-    </row>
-    <row r="831" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="R830" s="13"/>
+      <c r="S830" s="11"/>
+    </row>
+    <row r="831" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B831" t="s">
         <v>121</v>
       </c>
       <c r="C831">
         <v>5.9</v>
       </c>
-      <c r="O831" s="6"/>
+      <c r="O831" s="8"/>
       <c r="P831" s="2" t="s">
         <v>68</v>
       </c>
       <c r="Q831" s="2">
         <v>7</v>
       </c>
-      <c r="R831" s="9"/>
-    </row>
-    <row r="832" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="R831" s="13"/>
+      <c r="S831" s="11"/>
+    </row>
+    <row r="832" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B832" t="s">
         <v>130</v>
       </c>
       <c r="C832">
         <v>7.6</v>
       </c>
-      <c r="O832" s="6"/>
+      <c r="O832" s="8"/>
       <c r="P832" s="2" t="s">
         <v>69</v>
       </c>
       <c r="Q832" s="2">
         <v>7.5</v>
       </c>
-      <c r="R832" s="9"/>
-    </row>
-    <row r="833" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="R832" s="13"/>
+      <c r="S832" s="11"/>
+    </row>
+    <row r="833" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B833" t="s">
         <v>131</v>
       </c>
       <c r="C833">
         <v>4.3</v>
       </c>
-      <c r="O833" s="6"/>
+      <c r="O833" s="8"/>
       <c r="P833" s="2" t="s">
         <v>121</v>
       </c>
       <c r="Q833" s="2">
         <v>5.9</v>
       </c>
-      <c r="R833" s="9"/>
-    </row>
-    <row r="834" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="R833" s="13"/>
+      <c r="S833" s="11"/>
+    </row>
+    <row r="834" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B834" t="s">
         <v>134</v>
       </c>
       <c r="C834">
         <v>7.5</v>
       </c>
-      <c r="O834" s="6"/>
+      <c r="O834" s="8"/>
       <c r="P834" s="2" t="s">
         <v>130</v>
       </c>
       <c r="Q834" s="2">
         <v>7.6</v>
       </c>
-      <c r="R834" s="9"/>
-    </row>
-    <row r="835" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="R834" s="13"/>
+      <c r="S834" s="11"/>
+    </row>
+    <row r="835" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B835" t="s">
         <v>136</v>
       </c>
       <c r="C835">
         <v>7.4</v>
       </c>
-      <c r="O835" s="6"/>
+      <c r="O835" s="8"/>
       <c r="P835" s="2" t="s">
         <v>131</v>
       </c>
       <c r="Q835" s="2">
         <v>4.3</v>
       </c>
-      <c r="R835" s="9"/>
-    </row>
-    <row r="836" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="R835" s="13"/>
+      <c r="S835" s="11"/>
+    </row>
+    <row r="836" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A836" t="s">
         <v>138</v>
       </c>
@@ -11195,32 +14145,34 @@
         <f>MEDIAN(C836:C853)</f>
         <v>7.45</v>
       </c>
-      <c r="O836" s="6"/>
+      <c r="O836" s="8"/>
       <c r="P836" s="2" t="s">
         <v>134</v>
       </c>
       <c r="Q836" s="2">
         <v>7.5</v>
       </c>
-      <c r="R836" s="9"/>
-    </row>
-    <row r="837" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="R836" s="13"/>
+      <c r="S836" s="11"/>
+    </row>
+    <row r="837" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B837" t="s">
         <v>5</v>
       </c>
       <c r="C837">
         <v>8.1</v>
       </c>
-      <c r="O837" s="7"/>
+      <c r="O837" s="9"/>
       <c r="P837" s="2" t="s">
         <v>136</v>
       </c>
       <c r="Q837" s="2">
         <v>7.4</v>
       </c>
-      <c r="R837" s="10"/>
-    </row>
-    <row r="838" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="R837" s="13"/>
+      <c r="S837" s="12"/>
+    </row>
+    <row r="838" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B838" t="s">
         <v>14</v>
       </c>
@@ -11228,7 +14180,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="839" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="839" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B839" t="s">
         <v>19</v>
       </c>
@@ -11236,7 +14188,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="840" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="840" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B840" t="s">
         <v>23</v>
       </c>
@@ -11244,7 +14196,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="841" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="841" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B841" t="s">
         <v>26</v>
       </c>
@@ -11252,7 +14204,7 @@
         <v>5.3</v>
       </c>
     </row>
-    <row r="842" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="842" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B842" t="s">
         <v>27</v>
       </c>
@@ -11260,7 +14212,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="843" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="843" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B843" t="s">
         <v>28</v>
       </c>
@@ -11268,7 +14220,7 @@
         <v>5.3</v>
       </c>
     </row>
-    <row r="844" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="844" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B844" t="s">
         <v>30</v>
       </c>
@@ -11276,7 +14228,7 @@
         <v>6.1</v>
       </c>
     </row>
-    <row r="845" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="845" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B845" t="s">
         <v>41</v>
       </c>
@@ -11284,7 +14236,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="846" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="846" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B846" t="s">
         <v>46</v>
       </c>
@@ -11292,7 +14244,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="847" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="847" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B847" t="s">
         <v>68</v>
       </c>
@@ -11300,7 +14252,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="848" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="848" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B848" t="s">
         <v>69</v>
       </c>
@@ -37318,10 +40270,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="O820:O837"/>
+    <mergeCell ref="S820:S837"/>
     <mergeCell ref="R820:R837"/>
   </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>